--- a/manufacturing-warehouse-planning/仓库规划库存需求计算模板_七道工序版.xlsx
+++ b/manufacturing-warehouse-planning/仓库规划库存需求计算模板_七道工序版.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>自动按原料汇总日消耗量，并计算：
-设计库存 = MAX(日消耗×采购提前期, 最小订购量) + 安全库存 + 下批备料库存 + 退料库存 + 待检库存。</t>
+设计库存 = MAX(日消耗×有效采购提前期, MOQ, MPQ)×安全系数 + 安全库存 + 下批备料库存 + 退料库存 + 待检库存 - 旧料可消耗量。</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t>按工序位置和SKU 计算：
-设计WIP = MAX(下游小时消耗×缓冲小时数, 批量×最大等待批次数) + 待检库存 + 尾批库存 + 不良/返工库存。</t>
+设计WIP = 修正后基础WIP + 待检库存 + 尾批库存 + 不良/返工库存；其中修正后基础WIP考虑设备故障率与工序良率损失。</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       <c r="C10" s="4" t="inlineStr">
         <is>
           <t>按SKU 计算：
-设计库存 = MAX(日需求×生产间隔, 日需求×目标库存天数, 最小生产批量) + 安全库存 + 待检放行库存。</t>
+设计库存 = MAX(日需求×生产间隔, 日需求×目标库存天数, 最小生产批量) + 安全库存 + 返工补偿库存 + 待检放行库存。</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>关键假设，需要特别关注和确认。</t>
+          <t>当前模板未启用黄色专用输入样式，关键假设请优先检查参数设置中“需求与供应波动修正”分组。</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>库存 = MAX(日均消耗×采购提前期天数, 最小订购量MOQ) + 安全库存 + 下一批次备料库存 + 换产退料库存 + 待检库存</t>
+          <t>库存 = MAX(日均消耗×有效采购提前期天数, MOQ, MPQ)×安全系数 + 安全库存 + 下一批次备料 + 换产退料 + 待检库存 - 旧料可消耗量</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>库存 = MAX(下游小时消耗×缓冲小时数, 批量大小×最大等待批次数) + 待检等待库存 + 尾批库存 + 不良品/返工/隔离库存</t>
+          <t>库存 = MAX(下游小时消耗×缓冲小时数, 批量大小×最大等待批次数) ÷(1-故障率)×(1+良率损失率) + 待检等待库存 + 尾批库存 + 不良品/返工/隔离库存</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>库存 = MAX(日需求量×生产间隔天数, 日需求量×目标库存天数, 最小生产批量) + 安全库存天数×日需求量 + 待检放行库存</t>
+          <t>库存 = MAX(日需求量×生产间隔天数, 日需求量×目标库存天数, 最小生产批量) + 安全库存天数×日需求量 + 返工补偿库存 + 待检放行库存</t>
         </is>
       </c>
     </row>
@@ -883,22 +883,58 @@
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>安全系数</t>
+          <t>需求修正系数叠加</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>参数设置中的安全系数会乘以基础库存量，建议原料仓1.1~1.3，过程品仓1.1~1.2，成品仓1.1~1.2。</t>
+          <t>Q3/Q4峰值、订单变更冗余、新品爬坡系数会乘法叠加，请结合历史波动谨慎设值，避免过度放大。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="3" t="inlineStr">
         <is>
+          <t>动态安全库存</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>当前模板暂按固定安全库存计算（未启用动态算法）；后续有数据后可在参数设置中启用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>分层管理</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>当前模板未启用ABC/XYZ分层管理，建议后续有分层规则后再接入差异化安全库存。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>安全系数</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>参数设置中的安全系数会乘以基础库存量，建议原料仓1.1~1.3，过程品仓1.1~1.2，成品仓1.1~1.2。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
           <t>数量单位</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>本表不限定单位，请在各表表头的单位列中注明所使用的单位（件、箱、吨、kg等），并保持全表一致。</t>
         </is>
@@ -923,7 +959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1293,20 +1329,228 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="12" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>【需求与供应波动修正】</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Q3/Q4需求峰值系数</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>旺季需求放大系数，建议1.10~1.30（如仅部分SKU受影响，请在SKU层按需调整）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>订单变更/取消冗余系数</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>可参考历史呆滞库存占比估算，建议1.00~1.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>原料交期波动系数</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>用于放大基础采购提前期，覆盖供应商波动</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>春节停运附加天数</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>天</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>节假日停运可按15~21天预估</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>瓶颈设备故障率</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>按瓶颈工序设备故障率估算产能波动</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>石墨化良率损失率</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>石墨化工序低良率补偿参数，建议5%~15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>成品返工率</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>成品工序返工比例参数，建议5%~10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>新品爬坡系数</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>新品爬坡阶段需求修正系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>动态安全库存启用标记</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>当前默认0=未启用，后续有数据后可切换</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>ABC分层管理启用标记</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>当前默认0=未启用，后续分层管理后可切换</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>★ 其他工作表通过[参数设置!C行号]引用本表数值，请勿删除或移动行。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1514,11 +1758,11 @@
         <v>120000</v>
       </c>
       <c r="F3" s="10">
-        <f>IFERROR(产品SKU!E3/12,"")</f>
+        <f>IFERROR((产品SKU!E3/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G3" s="10">
-        <f>IFERROR(产品SKU!E3/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E3/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H3" s="9" t="n">
@@ -1588,11 +1832,11 @@
         <v>96000</v>
       </c>
       <c r="F4" s="10">
-        <f>IFERROR(产品SKU!E4/12,"")</f>
+        <f>IFERROR((产品SKU!E4/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>IFERROR(产品SKU!E4/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E4/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H4" s="9" t="n">
@@ -1662,11 +1906,11 @@
         <v>72000</v>
       </c>
       <c r="F5" s="10">
-        <f>IFERROR(产品SKU!E5/12,"")</f>
+        <f>IFERROR((产品SKU!E5/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G5" s="10">
-        <f>IFERROR(产品SKU!E5/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E5/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H5" s="9" t="n">
@@ -1736,11 +1980,11 @@
         <v>60000</v>
       </c>
       <c r="F6" s="10">
-        <f>IFERROR(产品SKU!E6/12,"")</f>
+        <f>IFERROR((产品SKU!E6/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>IFERROR(产品SKU!E6/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E6/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H6" s="9" t="n">
@@ -1810,11 +2054,11 @@
         <v>48000</v>
       </c>
       <c r="F7" s="10">
-        <f>IFERROR(产品SKU!E7/12,"")</f>
+        <f>IFERROR((产品SKU!E7/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>IFERROR(产品SKU!E7/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E7/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
@@ -1884,11 +2128,11 @@
         <v>36000</v>
       </c>
       <c r="F8" s="10">
-        <f>IFERROR(产品SKU!E8/12,"")</f>
+        <f>IFERROR((产品SKU!E8/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>IFERROR(产品SKU!E8/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E8/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
@@ -1958,11 +2202,11 @@
         <v>24000</v>
       </c>
       <c r="F9" s="10">
-        <f>IFERROR(产品SKU!E9/12,"")</f>
+        <f>IFERROR((产品SKU!E9/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G9" s="10">
-        <f>IFERROR(产品SKU!E9/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E9/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
@@ -2032,11 +2276,11 @@
         <v>18000</v>
       </c>
       <c r="F10" s="10">
-        <f>IFERROR(产品SKU!E10/12,"")</f>
+        <f>IFERROR((产品SKU!E10/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G10" s="10">
-        <f>IFERROR(产品SKU!E10/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E10/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H10" s="9" t="n">
@@ -2092,11 +2336,11 @@
       <c r="D11" s="14" t="n"/>
       <c r="E11" s="14" t="n"/>
       <c r="F11" s="10">
-        <f>IFERROR(产品SKU!E11/12,"")</f>
+        <f>IFERROR((产品SKU!E11/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G11" s="10">
-        <f>IFERROR(产品SKU!E11/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E11/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H11" s="14" t="n"/>
@@ -2124,11 +2368,11 @@
       <c r="D12" s="14" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="10">
-        <f>IFERROR(产品SKU!E12/12,"")</f>
+        <f>IFERROR((产品SKU!E12/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G12" s="10">
-        <f>IFERROR(产品SKU!E12/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E12/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H12" s="14" t="n"/>
@@ -2156,11 +2400,11 @@
       <c r="D13" s="14" t="n"/>
       <c r="E13" s="14" t="n"/>
       <c r="F13" s="10">
-        <f>IFERROR(产品SKU!E13/12,"")</f>
+        <f>IFERROR((产品SKU!E13/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G13" s="10">
-        <f>IFERROR(产品SKU!E13/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E13/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H13" s="14" t="n"/>
@@ -2188,11 +2432,11 @@
       <c r="D14" s="14" t="n"/>
       <c r="E14" s="14" t="n"/>
       <c r="F14" s="10">
-        <f>IFERROR(产品SKU!E14/12,"")</f>
+        <f>IFERROR((产品SKU!E14/12)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="G14" s="10">
-        <f>IFERROR(产品SKU!E14/参数设置!$C$4,"")</f>
+        <f>IFERROR((产品SKU!E14/参数设置!$C$4)*参数设置!$C$24*参数设置!$C$25*参数设置!$C$31,"")</f>
         <v/>
       </c>
       <c r="H14" s="14" t="n"/>
@@ -2807,7 +3051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2818,14 +3062,19 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2838,7 +3087,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>公式：设计库存 = MAX(日均消耗×采购提前期, MOQ) × 安全系数 + 安全库存 + 下批备料库存 + 换产退料库存 + 待检库存</t>
+          <t>公式：设计库存 = MAX(日均消耗×有效采购提前期, MOQ, MPQ) × 安全系数 + 安全库存 + 下批备料库存 + 换产退料库存 + 待检库存 - 呆滞旧料可消耗量</t>
         </is>
       </c>
     </row>
@@ -2871,62 +3120,93 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>采购提前期
-(天)</t>
+          <t>基础采购
+提前期(天)</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>春节停运
+附加天数</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>交期波动
+系数</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>有效采购
+提前期(天)
+[自动]</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>最小订购量
 MOQ</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>最小到货批量
+MPQ</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>安全系数</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>安全库存量
 (件)</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>下批备料
 库存量</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>换产退料
 库存量</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>待检库存量</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>呆滞旧料
+可消耗量</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>设计库存量
 [自动]</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="S3" s="6" t="inlineStr">
         <is>
           <t>每托盘装量</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="T3" s="6" t="inlineStr">
         <is>
           <t>设计托盘数
 [自动]</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="U3" s="6" t="inlineStr">
         <is>
           <t>估算占地面积
 (m²)[自动]</t>
@@ -2956,26 +3236,40 @@
       <c r="F4" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="G4" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H4" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I4" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I4" s="10">
+        <f>IFERROR((原料仓计算!F4*原料仓计算!H4)+原料仓计算!G4,0)</f>
+        <v/>
+      </c>
       <c r="J4" s="9" t="n"/>
       <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="10">
-        <f>IFERROR(MAX(原料仓计算!E4*原料仓计算!F4,IF(原料仓计算!G4="",0,原料仓计算!G4))*原料仓计算!H4+IF(原料仓计算!I4="",0,原料仓计算!I4)+IF(原料仓计算!J4="",0,原料仓计算!J4)+IF(原料仓计算!K4="",0,原料仓计算!K4)+IF(原料仓计算!L4="",0,原料仓计算!L4),0)</f>
-        <v/>
-      </c>
+      <c r="L4" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M4" s="9" t="n"/>
       <c r="N4" s="9" t="n"/>
-      <c r="O4" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M4/IF(原料仓计算!N4=0,1,原料仓计算!N4),1),0)</f>
-        <v/>
-      </c>
-      <c r="P4" s="10">
-        <f>IFERROR(原料仓计算!O4*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O4" s="9" t="n"/>
+      <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="9" t="n"/>
+      <c r="R4" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E4*原料仓计算!I4,IF(原料仓计算!J4="",0,原料仓计算!J4),IF(原料仓计算!K4="",0,原料仓计算!K4))*原料仓计算!L4+IF(原料仓计算!M4="",0,原料仓计算!M4)+IF(原料仓计算!N4="",0,原料仓计算!N4)+IF(原料仓计算!O4="",0,原料仓计算!O4)+IF(原料仓计算!P4="",0,原料仓计算!P4)-IF(原料仓计算!Q4="",0,原料仓计算!Q4)),0)</f>
+        <v/>
+      </c>
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R4/IF(原料仓计算!S4=0,1,原料仓计算!S4),1),0)</f>
+        <v/>
+      </c>
+      <c r="U4" s="10">
+        <f>IFERROR(原料仓计算!T4*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3002,26 +3296,40 @@
       <c r="F5" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="9" t="n"/>
+      <c r="G5" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H5" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I5" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I5" s="10">
+        <f>IFERROR((原料仓计算!F5*原料仓计算!H5)+原料仓计算!G5,0)</f>
+        <v/>
+      </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="10">
-        <f>IFERROR(MAX(原料仓计算!E5*原料仓计算!F5,IF(原料仓计算!G5="",0,原料仓计算!G5))*原料仓计算!H5+IF(原料仓计算!I5="",0,原料仓计算!I5)+IF(原料仓计算!J5="",0,原料仓计算!J5)+IF(原料仓计算!K5="",0,原料仓计算!K5)+IF(原料仓计算!L5="",0,原料仓计算!L5),0)</f>
-        <v/>
-      </c>
+      <c r="L5" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
-      <c r="O5" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M5/IF(原料仓计算!N5=0,1,原料仓计算!N5),1),0)</f>
-        <v/>
-      </c>
-      <c r="P5" s="10">
-        <f>IFERROR(原料仓计算!O5*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E5*原料仓计算!I5,IF(原料仓计算!J5="",0,原料仓计算!J5),IF(原料仓计算!K5="",0,原料仓计算!K5))*原料仓计算!L5+IF(原料仓计算!M5="",0,原料仓计算!M5)+IF(原料仓计算!N5="",0,原料仓计算!N5)+IF(原料仓计算!O5="",0,原料仓计算!O5)+IF(原料仓计算!P5="",0,原料仓计算!P5)-IF(原料仓计算!Q5="",0,原料仓计算!Q5)),0)</f>
+        <v/>
+      </c>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R5/IF(原料仓计算!S5=0,1,原料仓计算!S5),1),0)</f>
+        <v/>
+      </c>
+      <c r="U5" s="10">
+        <f>IFERROR(原料仓计算!T5*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3048,26 +3356,40 @@
       <c r="F6" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="G6" s="9" t="n"/>
+      <c r="G6" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H6" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I6" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I6" s="10">
+        <f>IFERROR((原料仓计算!F6*原料仓计算!H6)+原料仓计算!G6,0)</f>
+        <v/>
+      </c>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="10">
-        <f>IFERROR(MAX(原料仓计算!E6*原料仓计算!F6,IF(原料仓计算!G6="",0,原料仓计算!G6))*原料仓计算!H6+IF(原料仓计算!I6="",0,原料仓计算!I6)+IF(原料仓计算!J6="",0,原料仓计算!J6)+IF(原料仓计算!K6="",0,原料仓计算!K6)+IF(原料仓计算!L6="",0,原料仓计算!L6),0)</f>
-        <v/>
-      </c>
+      <c r="L6" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M6" s="9" t="n"/>
       <c r="N6" s="9" t="n"/>
-      <c r="O6" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M6/IF(原料仓计算!N6=0,1,原料仓计算!N6),1),0)</f>
-        <v/>
-      </c>
-      <c r="P6" s="10">
-        <f>IFERROR(原料仓计算!O6*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E6*原料仓计算!I6,IF(原料仓计算!J6="",0,原料仓计算!J6),IF(原料仓计算!K6="",0,原料仓计算!K6))*原料仓计算!L6+IF(原料仓计算!M6="",0,原料仓计算!M6)+IF(原料仓计算!N6="",0,原料仓计算!N6)+IF(原料仓计算!O6="",0,原料仓计算!O6)+IF(原料仓计算!P6="",0,原料仓计算!P6)-IF(原料仓计算!Q6="",0,原料仓计算!Q6)),0)</f>
+        <v/>
+      </c>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R6/IF(原料仓计算!S6=0,1,原料仓计算!S6),1),0)</f>
+        <v/>
+      </c>
+      <c r="U6" s="10">
+        <f>IFERROR(原料仓计算!T6*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3094,26 +3416,40 @@
       <c r="F7" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="G7" s="9" t="n"/>
+      <c r="G7" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H7" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I7" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I7" s="10">
+        <f>IFERROR((原料仓计算!F7*原料仓计算!H7)+原料仓计算!G7,0)</f>
+        <v/>
+      </c>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="10">
-        <f>IFERROR(MAX(原料仓计算!E7*原料仓计算!F7,IF(原料仓计算!G7="",0,原料仓计算!G7))*原料仓计算!H7+IF(原料仓计算!I7="",0,原料仓计算!I7)+IF(原料仓计算!J7="",0,原料仓计算!J7)+IF(原料仓计算!K7="",0,原料仓计算!K7)+IF(原料仓计算!L7="",0,原料仓计算!L7),0)</f>
-        <v/>
-      </c>
+      <c r="L7" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
-      <c r="O7" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M7/IF(原料仓计算!N7=0,1,原料仓计算!N7),1),0)</f>
-        <v/>
-      </c>
-      <c r="P7" s="10">
-        <f>IFERROR(原料仓计算!O7*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
+      <c r="R7" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E7*原料仓计算!I7,IF(原料仓计算!J7="",0,原料仓计算!J7),IF(原料仓计算!K7="",0,原料仓计算!K7))*原料仓计算!L7+IF(原料仓计算!M7="",0,原料仓计算!M7)+IF(原料仓计算!N7="",0,原料仓计算!N7)+IF(原料仓计算!O7="",0,原料仓计算!O7)+IF(原料仓计算!P7="",0,原料仓计算!P7)-IF(原料仓计算!Q7="",0,原料仓计算!Q7)),0)</f>
+        <v/>
+      </c>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R7/IF(原料仓计算!S7=0,1,原料仓计算!S7),1),0)</f>
+        <v/>
+      </c>
+      <c r="U7" s="10">
+        <f>IFERROR(原料仓计算!T7*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3140,26 +3476,40 @@
       <c r="F8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="G8" s="9" t="n"/>
+      <c r="G8" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H8" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I8" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I8" s="10">
+        <f>IFERROR((原料仓计算!F8*原料仓计算!H8)+原料仓计算!G8,0)</f>
+        <v/>
+      </c>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="10">
-        <f>IFERROR(MAX(原料仓计算!E8*原料仓计算!F8,IF(原料仓计算!G8="",0,原料仓计算!G8))*原料仓计算!H8+IF(原料仓计算!I8="",0,原料仓计算!I8)+IF(原料仓计算!J8="",0,原料仓计算!J8)+IF(原料仓计算!K8="",0,原料仓计算!K8)+IF(原料仓计算!L8="",0,原料仓计算!L8),0)</f>
-        <v/>
-      </c>
+      <c r="L8" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M8" s="9" t="n"/>
       <c r="N8" s="9" t="n"/>
-      <c r="O8" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M8/IF(原料仓计算!N8=0,1,原料仓计算!N8),1),0)</f>
-        <v/>
-      </c>
-      <c r="P8" s="10">
-        <f>IFERROR(原料仓计算!O8*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E8*原料仓计算!I8,IF(原料仓计算!J8="",0,原料仓计算!J8),IF(原料仓计算!K8="",0,原料仓计算!K8))*原料仓计算!L8+IF(原料仓计算!M8="",0,原料仓计算!M8)+IF(原料仓计算!N8="",0,原料仓计算!N8)+IF(原料仓计算!O8="",0,原料仓计算!O8)+IF(原料仓计算!P8="",0,原料仓计算!P8)-IF(原料仓计算!Q8="",0,原料仓计算!Q8)),0)</f>
+        <v/>
+      </c>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R8/IF(原料仓计算!S8=0,1,原料仓计算!S8),1),0)</f>
+        <v/>
+      </c>
+      <c r="U8" s="10">
+        <f>IFERROR(原料仓计算!T8*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3186,26 +3536,40 @@
       <c r="F9" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="G9" s="9" t="n"/>
+      <c r="G9" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H9" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I9" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I9" s="10">
+        <f>IFERROR((原料仓计算!F9*原料仓计算!H9)+原料仓计算!G9,0)</f>
+        <v/>
+      </c>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="10">
-        <f>IFERROR(MAX(原料仓计算!E9*原料仓计算!F9,IF(原料仓计算!G9="",0,原料仓计算!G9))*原料仓计算!H9+IF(原料仓计算!I9="",0,原料仓计算!I9)+IF(原料仓计算!J9="",0,原料仓计算!J9)+IF(原料仓计算!K9="",0,原料仓计算!K9)+IF(原料仓计算!L9="",0,原料仓计算!L9),0)</f>
-        <v/>
-      </c>
+      <c r="L9" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
-      <c r="O9" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M9/IF(原料仓计算!N9=0,1,原料仓计算!N9),1),0)</f>
-        <v/>
-      </c>
-      <c r="P9" s="10">
-        <f>IFERROR(原料仓计算!O9*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E9*原料仓计算!I9,IF(原料仓计算!J9="",0,原料仓计算!J9),IF(原料仓计算!K9="",0,原料仓计算!K9))*原料仓计算!L9+IF(原料仓计算!M9="",0,原料仓计算!M9)+IF(原料仓计算!N9="",0,原料仓计算!N9)+IF(原料仓计算!O9="",0,原料仓计算!O9)+IF(原料仓计算!P9="",0,原料仓计算!P9)-IF(原料仓计算!Q9="",0,原料仓计算!Q9)),0)</f>
+        <v/>
+      </c>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R9/IF(原料仓计算!S9=0,1,原料仓计算!S9),1),0)</f>
+        <v/>
+      </c>
+      <c r="U9" s="10">
+        <f>IFERROR(原料仓计算!T9*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3232,26 +3596,40 @@
       <c r="F10" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="G10" s="9" t="n"/>
+      <c r="G10" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H10" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I10" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I10" s="10">
+        <f>IFERROR((原料仓计算!F10*原料仓计算!H10)+原料仓计算!G10,0)</f>
+        <v/>
+      </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="10">
-        <f>IFERROR(MAX(原料仓计算!E10*原料仓计算!F10,IF(原料仓计算!G10="",0,原料仓计算!G10))*原料仓计算!H10+IF(原料仓计算!I10="",0,原料仓计算!I10)+IF(原料仓计算!J10="",0,原料仓计算!J10)+IF(原料仓计算!K10="",0,原料仓计算!K10)+IF(原料仓计算!L10="",0,原料仓计算!L10),0)</f>
-        <v/>
-      </c>
+      <c r="L10" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
-      <c r="O10" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M10/IF(原料仓计算!N10=0,1,原料仓计算!N10),1),0)</f>
-        <v/>
-      </c>
-      <c r="P10" s="10">
-        <f>IFERROR(原料仓计算!O10*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E10*原料仓计算!I10,IF(原料仓计算!J10="",0,原料仓计算!J10),IF(原料仓计算!K10="",0,原料仓计算!K10))*原料仓计算!L10+IF(原料仓计算!M10="",0,原料仓计算!M10)+IF(原料仓计算!N10="",0,原料仓计算!N10)+IF(原料仓计算!O10="",0,原料仓计算!O10)+IF(原料仓计算!P10="",0,原料仓计算!P10)-IF(原料仓计算!Q10="",0,原料仓计算!Q10)),0)</f>
+        <v/>
+      </c>
+      <c r="S10" s="9" t="n"/>
+      <c r="T10" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R10/IF(原料仓计算!S10=0,1,原料仓计算!S10),1),0)</f>
+        <v/>
+      </c>
+      <c r="U10" s="10">
+        <f>IFERROR(原料仓计算!T10*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3278,26 +3656,40 @@
       <c r="F11" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="G11" s="9" t="n"/>
+      <c r="G11" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H11" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I11" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I11" s="10">
+        <f>IFERROR((原料仓计算!F11*原料仓计算!H11)+原料仓计算!G11,0)</f>
+        <v/>
+      </c>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="10">
-        <f>IFERROR(MAX(原料仓计算!E11*原料仓计算!F11,IF(原料仓计算!G11="",0,原料仓计算!G11))*原料仓计算!H11+IF(原料仓计算!I11="",0,原料仓计算!I11)+IF(原料仓计算!J11="",0,原料仓计算!J11)+IF(原料仓计算!K11="",0,原料仓计算!K11)+IF(原料仓计算!L11="",0,原料仓计算!L11),0)</f>
-        <v/>
-      </c>
+      <c r="L11" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
-      <c r="O11" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M11/IF(原料仓计算!N11=0,1,原料仓计算!N11),1),0)</f>
-        <v/>
-      </c>
-      <c r="P11" s="10">
-        <f>IFERROR(原料仓计算!O11*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E11*原料仓计算!I11,IF(原料仓计算!J11="",0,原料仓计算!J11),IF(原料仓计算!K11="",0,原料仓计算!K11))*原料仓计算!L11+IF(原料仓计算!M11="",0,原料仓计算!M11)+IF(原料仓计算!N11="",0,原料仓计算!N11)+IF(原料仓计算!O11="",0,原料仓计算!O11)+IF(原料仓计算!P11="",0,原料仓计算!P11)-IF(原料仓计算!Q11="",0,原料仓计算!Q11)),0)</f>
+        <v/>
+      </c>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R11/IF(原料仓计算!S11=0,1,原料仓计算!S11),1),0)</f>
+        <v/>
+      </c>
+      <c r="U11" s="10">
+        <f>IFERROR(原料仓计算!T11*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3322,26 +3714,40 @@
         <v/>
       </c>
       <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
+      <c r="G12" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H12" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I12" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I12" s="10">
+        <f>IFERROR((原料仓计算!F12*原料仓计算!H12)+原料仓计算!G12,0)</f>
+        <v/>
+      </c>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="10">
-        <f>IFERROR(MAX(原料仓计算!E12*原料仓计算!F12,IF(原料仓计算!G12="",0,原料仓计算!G12))*原料仓计算!H12+IF(原料仓计算!I12="",0,原料仓计算!I12)+IF(原料仓计算!J12="",0,原料仓计算!J12)+IF(原料仓计算!K12="",0,原料仓计算!K12)+IF(原料仓计算!L12="",0,原料仓计算!L12),0)</f>
-        <v/>
-      </c>
+      <c r="L12" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M12" s="9" t="n"/>
       <c r="N12" s="9" t="n"/>
-      <c r="O12" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M12/IF(原料仓计算!N12=0,1,原料仓计算!N12),1),0)</f>
-        <v/>
-      </c>
-      <c r="P12" s="10">
-        <f>IFERROR(原料仓计算!O12*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O12" s="9" t="n"/>
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
+      <c r="R12" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E12*原料仓计算!I12,IF(原料仓计算!J12="",0,原料仓计算!J12),IF(原料仓计算!K12="",0,原料仓计算!K12))*原料仓计算!L12+IF(原料仓计算!M12="",0,原料仓计算!M12)+IF(原料仓计算!N12="",0,原料仓计算!N12)+IF(原料仓计算!O12="",0,原料仓计算!O12)+IF(原料仓计算!P12="",0,原料仓计算!P12)-IF(原料仓计算!Q12="",0,原料仓计算!Q12)),0)</f>
+        <v/>
+      </c>
+      <c r="S12" s="9" t="n"/>
+      <c r="T12" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R12/IF(原料仓计算!S12=0,1,原料仓计算!S12),1),0)</f>
+        <v/>
+      </c>
+      <c r="U12" s="10">
+        <f>IFERROR(原料仓计算!T12*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3366,26 +3772,40 @@
         <v/>
       </c>
       <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
+      <c r="G13" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H13" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I13" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I13" s="10">
+        <f>IFERROR((原料仓计算!F13*原料仓计算!H13)+原料仓计算!G13,0)</f>
+        <v/>
+      </c>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="10">
-        <f>IFERROR(MAX(原料仓计算!E13*原料仓计算!F13,IF(原料仓计算!G13="",0,原料仓计算!G13))*原料仓计算!H13+IF(原料仓计算!I13="",0,原料仓计算!I13)+IF(原料仓计算!J13="",0,原料仓计算!J13)+IF(原料仓计算!K13="",0,原料仓计算!K13)+IF(原料仓计算!L13="",0,原料仓计算!L13),0)</f>
-        <v/>
-      </c>
+      <c r="L13" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
-      <c r="O13" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M13/IF(原料仓计算!N13=0,1,原料仓计算!N13),1),0)</f>
-        <v/>
-      </c>
-      <c r="P13" s="10">
-        <f>IFERROR(原料仓计算!O13*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O13" s="9" t="n"/>
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E13*原料仓计算!I13,IF(原料仓计算!J13="",0,原料仓计算!J13),IF(原料仓计算!K13="",0,原料仓计算!K13))*原料仓计算!L13+IF(原料仓计算!M13="",0,原料仓计算!M13)+IF(原料仓计算!N13="",0,原料仓计算!N13)+IF(原料仓计算!O13="",0,原料仓计算!O13)+IF(原料仓计算!P13="",0,原料仓计算!P13)-IF(原料仓计算!Q13="",0,原料仓计算!Q13)),0)</f>
+        <v/>
+      </c>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R13/IF(原料仓计算!S13=0,1,原料仓计算!S13),1),0)</f>
+        <v/>
+      </c>
+      <c r="U13" s="10">
+        <f>IFERROR(原料仓计算!T13*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3410,26 +3830,40 @@
         <v/>
       </c>
       <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
+      <c r="G14" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H14" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I14" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I14" s="10">
+        <f>IFERROR((原料仓计算!F14*原料仓计算!H14)+原料仓计算!G14,0)</f>
+        <v/>
+      </c>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="10">
-        <f>IFERROR(MAX(原料仓计算!E14*原料仓计算!F14,IF(原料仓计算!G14="",0,原料仓计算!G14))*原料仓计算!H14+IF(原料仓计算!I14="",0,原料仓计算!I14)+IF(原料仓计算!J14="",0,原料仓计算!J14)+IF(原料仓计算!K14="",0,原料仓计算!K14)+IF(原料仓计算!L14="",0,原料仓计算!L14),0)</f>
-        <v/>
-      </c>
+      <c r="L14" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M14" s="9" t="n"/>
       <c r="N14" s="9" t="n"/>
-      <c r="O14" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M14/IF(原料仓计算!N14=0,1,原料仓计算!N14),1),0)</f>
-        <v/>
-      </c>
-      <c r="P14" s="10">
-        <f>IFERROR(原料仓计算!O14*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="9" t="n"/>
+      <c r="R14" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E14*原料仓计算!I14,IF(原料仓计算!J14="",0,原料仓计算!J14),IF(原料仓计算!K14="",0,原料仓计算!K14))*原料仓计算!L14+IF(原料仓计算!M14="",0,原料仓计算!M14)+IF(原料仓计算!N14="",0,原料仓计算!N14)+IF(原料仓计算!O14="",0,原料仓计算!O14)+IF(原料仓计算!P14="",0,原料仓计算!P14)-IF(原料仓计算!Q14="",0,原料仓计算!Q14)),0)</f>
+        <v/>
+      </c>
+      <c r="S14" s="9" t="n"/>
+      <c r="T14" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R14/IF(原料仓计算!S14=0,1,原料仓计算!S14),1),0)</f>
+        <v/>
+      </c>
+      <c r="U14" s="10">
+        <f>IFERROR(原料仓计算!T14*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3454,26 +3888,40 @@
         <v/>
       </c>
       <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
+      <c r="G15" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H15" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I15" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I15" s="10">
+        <f>IFERROR((原料仓计算!F15*原料仓计算!H15)+原料仓计算!G15,0)</f>
+        <v/>
+      </c>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="10">
-        <f>IFERROR(MAX(原料仓计算!E15*原料仓计算!F15,IF(原料仓计算!G15="",0,原料仓计算!G15))*原料仓计算!H15+IF(原料仓计算!I15="",0,原料仓计算!I15)+IF(原料仓计算!J15="",0,原料仓计算!J15)+IF(原料仓计算!K15="",0,原料仓计算!K15)+IF(原料仓计算!L15="",0,原料仓计算!L15),0)</f>
-        <v/>
-      </c>
+      <c r="L15" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
-      <c r="O15" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M15/IF(原料仓计算!N15=0,1,原料仓计算!N15),1),0)</f>
-        <v/>
-      </c>
-      <c r="P15" s="10">
-        <f>IFERROR(原料仓计算!O15*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E15*原料仓计算!I15,IF(原料仓计算!J15="",0,原料仓计算!J15),IF(原料仓计算!K15="",0,原料仓计算!K15))*原料仓计算!L15+IF(原料仓计算!M15="",0,原料仓计算!M15)+IF(原料仓计算!N15="",0,原料仓计算!N15)+IF(原料仓计算!O15="",0,原料仓计算!O15)+IF(原料仓计算!P15="",0,原料仓计算!P15)-IF(原料仓计算!Q15="",0,原料仓计算!Q15)),0)</f>
+        <v/>
+      </c>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R15/IF(原料仓计算!S15=0,1,原料仓计算!S15),1),0)</f>
+        <v/>
+      </c>
+      <c r="U15" s="10">
+        <f>IFERROR(原料仓计算!T15*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3498,26 +3946,40 @@
         <v/>
       </c>
       <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
+      <c r="G16" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H16" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I16" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I16" s="10">
+        <f>IFERROR((原料仓计算!F16*原料仓计算!H16)+原料仓计算!G16,0)</f>
+        <v/>
+      </c>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="10">
-        <f>IFERROR(MAX(原料仓计算!E16*原料仓计算!F16,IF(原料仓计算!G16="",0,原料仓计算!G16))*原料仓计算!H16+IF(原料仓计算!I16="",0,原料仓计算!I16)+IF(原料仓计算!J16="",0,原料仓计算!J16)+IF(原料仓计算!K16="",0,原料仓计算!K16)+IF(原料仓计算!L16="",0,原料仓计算!L16),0)</f>
-        <v/>
-      </c>
+      <c r="L16" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M16" s="9" t="n"/>
       <c r="N16" s="9" t="n"/>
-      <c r="O16" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M16/IF(原料仓计算!N16=0,1,原料仓计算!N16),1),0)</f>
-        <v/>
-      </c>
-      <c r="P16" s="10">
-        <f>IFERROR(原料仓计算!O16*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E16*原料仓计算!I16,IF(原料仓计算!J16="",0,原料仓计算!J16),IF(原料仓计算!K16="",0,原料仓计算!K16))*原料仓计算!L16+IF(原料仓计算!M16="",0,原料仓计算!M16)+IF(原料仓计算!N16="",0,原料仓计算!N16)+IF(原料仓计算!O16="",0,原料仓计算!O16)+IF(原料仓计算!P16="",0,原料仓计算!P16)-IF(原料仓计算!Q16="",0,原料仓计算!Q16)),0)</f>
+        <v/>
+      </c>
+      <c r="S16" s="9" t="n"/>
+      <c r="T16" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R16/IF(原料仓计算!S16=0,1,原料仓计算!S16),1),0)</f>
+        <v/>
+      </c>
+      <c r="U16" s="10">
+        <f>IFERROR(原料仓计算!T16*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3542,26 +4004,40 @@
         <v/>
       </c>
       <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
+      <c r="G17" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H17" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I17" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I17" s="10">
+        <f>IFERROR((原料仓计算!F17*原料仓计算!H17)+原料仓计算!G17,0)</f>
+        <v/>
+      </c>
       <c r="J17" s="9" t="n"/>
       <c r="K17" s="9" t="n"/>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="10">
-        <f>IFERROR(MAX(原料仓计算!E17*原料仓计算!F17,IF(原料仓计算!G17="",0,原料仓计算!G17))*原料仓计算!H17+IF(原料仓计算!I17="",0,原料仓计算!I17)+IF(原料仓计算!J17="",0,原料仓计算!J17)+IF(原料仓计算!K17="",0,原料仓计算!K17)+IF(原料仓计算!L17="",0,原料仓计算!L17),0)</f>
-        <v/>
-      </c>
+      <c r="L17" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
-      <c r="O17" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M17/IF(原料仓计算!N17=0,1,原料仓计算!N17),1),0)</f>
-        <v/>
-      </c>
-      <c r="P17" s="10">
-        <f>IFERROR(原料仓计算!O17*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E17*原料仓计算!I17,IF(原料仓计算!J17="",0,原料仓计算!J17),IF(原料仓计算!K17="",0,原料仓计算!K17))*原料仓计算!L17+IF(原料仓计算!M17="",0,原料仓计算!M17)+IF(原料仓计算!N17="",0,原料仓计算!N17)+IF(原料仓计算!O17="",0,原料仓计算!O17)+IF(原料仓计算!P17="",0,原料仓计算!P17)-IF(原料仓计算!Q17="",0,原料仓计算!Q17)),0)</f>
+        <v/>
+      </c>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R17/IF(原料仓计算!S17=0,1,原料仓计算!S17),1),0)</f>
+        <v/>
+      </c>
+      <c r="U17" s="10">
+        <f>IFERROR(原料仓计算!T17*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3586,26 +4062,40 @@
         <v/>
       </c>
       <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9" t="n"/>
+      <c r="G18" s="17">
+        <f>参数设置!$C$27</f>
+        <v/>
+      </c>
       <c r="H18" s="10">
-        <f>参数设置!$C$7</f>
-        <v/>
-      </c>
-      <c r="I18" s="9" t="n"/>
+        <f>参数设置!$C$26</f>
+        <v/>
+      </c>
+      <c r="I18" s="10">
+        <f>IFERROR((原料仓计算!F18*原料仓计算!H18)+原料仓计算!G18,0)</f>
+        <v/>
+      </c>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="9" t="n"/>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="10">
-        <f>IFERROR(MAX(原料仓计算!E18*原料仓计算!F18,IF(原料仓计算!G18="",0,原料仓计算!G18))*原料仓计算!H18+IF(原料仓计算!I18="",0,原料仓计算!I18)+IF(原料仓计算!J18="",0,原料仓计算!J18)+IF(原料仓计算!K18="",0,原料仓计算!K18)+IF(原料仓计算!L18="",0,原料仓计算!L18),0)</f>
-        <v/>
-      </c>
+      <c r="L18" s="10">
+        <f>参数设置!$C$7</f>
+        <v/>
+      </c>
+      <c r="M18" s="9" t="n"/>
       <c r="N18" s="9" t="n"/>
-      <c r="O18" s="17">
-        <f>IFERROR(CEILING(原料仓计算!M18/IF(原料仓计算!N18=0,1,原料仓计算!N18),1),0)</f>
-        <v/>
-      </c>
-      <c r="P18" s="10">
-        <f>IFERROR(原料仓计算!O18*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="10">
+        <f>IFERROR(MAX(0,MAX(原料仓计算!E18*原料仓计算!I18,IF(原料仓计算!J18="",0,原料仓计算!J18),IF(原料仓计算!K18="",0,原料仓计算!K18))*原料仓计算!L18+IF(原料仓计算!M18="",0,原料仓计算!M18)+IF(原料仓计算!N18="",0,原料仓计算!N18)+IF(原料仓计算!O18="",0,原料仓计算!O18)+IF(原料仓计算!P18="",0,原料仓计算!P18)-IF(原料仓计算!Q18="",0,原料仓计算!Q18)),0)</f>
+        <v/>
+      </c>
+      <c r="S18" s="9" t="n"/>
+      <c r="T18" s="17">
+        <f>IFERROR(CEILING(原料仓计算!R18/IF(原料仓计算!S18=0,1,原料仓计算!S18),1),0)</f>
+        <v/>
+      </c>
+      <c r="U18" s="10">
+        <f>IFERROR(原料仓计算!T18*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$17*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3615,24 +4105,24 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="M19" s="10">
-        <f>SUM(M4:M18)</f>
-        <v/>
-      </c>
-      <c r="O19" s="17">
-        <f>SUM(O4:O18)</f>
-        <v/>
-      </c>
-      <c r="P19" s="10">
-        <f>SUM(P4:P18)</f>
+      <c r="R19" s="10">
+        <f>SUM(R4:R18)</f>
+        <v/>
+      </c>
+      <c r="T19" s="17">
+        <f>SUM(T4:T18)</f>
+        <v/>
+      </c>
+      <c r="U19" s="10">
+        <f>SUM(U4:U18)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:U1"/>
     <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3645,7 +4135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q102"/>
+  <dimension ref="A1:S102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3660,11 +4150,13 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3677,7 +4169,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>公式：设计WIP = MAX(下游小时消耗×缓冲小时数, 批量×最大等待批次数) + 待检库存 + 尾批库存 + 不良品/返工/隔离库存</t>
+          <t>公式：设计WIP = MAX(下游小时消耗×缓冲小时数, 批量×最大等待批次数)÷(1-设备故障率)×(1+良率损失率) + 待检库存 + 尾批库存 + 不良品/返工/隔离库存</t>
         </is>
       </c>
     </row>
@@ -3748,36 +4240,46 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>设计基础WIP
-=MAX(...)
+          <t>修正后基础WIP
 [自动]</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>设备故障率</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>工序良率
+损失率</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>待检等待
 库存</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>尾批库存</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>不良/返工/
 隔离库存</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>设计WIP
 合计
 [自动]</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="S3" s="6" t="inlineStr">
         <is>
           <t>估算占地
 面积(m²)
@@ -3834,18 +4336,24 @@
         <v/>
       </c>
       <c r="L5" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H5,过程品仓计算!K5),0)</f>
-        <v/>
-      </c>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H5,过程品仓计算!K5)/MAX(1-IF(过程品仓计算!M5="",0,过程品仓计算!M5),0.01)*(1+IF(过程品仓计算!N5="",0,过程品仓计算!N5)),0)</f>
+        <v/>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O5" s="9" t="n"/>
-      <c r="P5" s="10">
-        <f>IFERROR(过程品仓计算!L5+IF(过程品仓计算!M5="",0,过程品仓计算!M5)+IF(过程品仓计算!N5="",0,过程品仓计算!N5)+IF(过程品仓计算!O5="",0,过程品仓计算!O5),0)</f>
-        <v/>
-      </c>
-      <c r="Q5" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P5/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="10">
+        <f>IFERROR(过程品仓计算!L5+IF(过程品仓计算!O5="",0,过程品仓计算!O5)+IF(过程品仓计算!P5="",0,过程品仓计算!P5)+IF(过程品仓计算!Q5="",0,过程品仓计算!Q5),0)</f>
+        <v/>
+      </c>
+      <c r="S5" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R5/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3891,18 +4399,24 @@
         <v/>
       </c>
       <c r="L6" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H6,过程品仓计算!K6),0)</f>
-        <v/>
-      </c>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H6,过程品仓计算!K6)/MAX(1-IF(过程品仓计算!M6="",0,过程品仓计算!M6),0.01)*(1+IF(过程品仓计算!N6="",0,过程品仓计算!N6)),0)</f>
+        <v/>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O6" s="9" t="n"/>
-      <c r="P6" s="10">
-        <f>IFERROR(过程品仓计算!L6+IF(过程品仓计算!M6="",0,过程品仓计算!M6)+IF(过程品仓计算!N6="",0,过程品仓计算!N6)+IF(过程品仓计算!O6="",0,过程品仓计算!O6),0)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P6/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="10">
+        <f>IFERROR(过程品仓计算!L6+IF(过程品仓计算!O6="",0,过程品仓计算!O6)+IF(过程品仓计算!P6="",0,过程品仓计算!P6)+IF(过程品仓计算!Q6="",0,过程品仓计算!Q6),0)</f>
+        <v/>
+      </c>
+      <c r="S6" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R6/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -3948,18 +4462,24 @@
         <v/>
       </c>
       <c r="L7" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H7,过程品仓计算!K7),0)</f>
-        <v/>
-      </c>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H7,过程品仓计算!K7)/MAX(1-IF(过程品仓计算!M7="",0,过程品仓计算!M7),0.01)*(1+IF(过程品仓计算!N7="",0,过程品仓计算!N7)),0)</f>
+        <v/>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O7" s="9" t="n"/>
-      <c r="P7" s="10">
-        <f>IFERROR(过程品仓计算!L7+IF(过程品仓计算!M7="",0,过程品仓计算!M7)+IF(过程品仓计算!N7="",0,过程品仓计算!N7)+IF(过程品仓计算!O7="",0,过程品仓计算!O7),0)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P7/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
+      <c r="R7" s="10">
+        <f>IFERROR(过程品仓计算!L7+IF(过程品仓计算!O7="",0,过程品仓计算!O7)+IF(过程品仓计算!P7="",0,过程品仓计算!P7)+IF(过程品仓计算!Q7="",0,过程品仓计算!Q7),0)</f>
+        <v/>
+      </c>
+      <c r="S7" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R7/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4005,18 +4525,24 @@
         <v/>
       </c>
       <c r="L8" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H8,过程品仓计算!K8),0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H8,过程品仓计算!K8)/MAX(1-IF(过程品仓计算!M8="",0,过程品仓计算!M8),0.01)*(1+IF(过程品仓计算!N8="",0,过程品仓计算!N8)),0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O8" s="9" t="n"/>
-      <c r="P8" s="10">
-        <f>IFERROR(过程品仓计算!L8+IF(过程品仓计算!M8="",0,过程品仓计算!M8)+IF(过程品仓计算!N8="",0,过程品仓计算!N8)+IF(过程品仓计算!O8="",0,过程品仓计算!O8),0)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P8/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="10">
+        <f>IFERROR(过程品仓计算!L8+IF(过程品仓计算!O8="",0,过程品仓计算!O8)+IF(过程品仓计算!P8="",0,过程品仓计算!P8)+IF(过程品仓计算!Q8="",0,过程品仓计算!Q8),0)</f>
+        <v/>
+      </c>
+      <c r="S8" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R8/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4062,18 +4588,24 @@
         <v/>
       </c>
       <c r="L9" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H9,过程品仓计算!K9),0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H9,过程品仓计算!K9)/MAX(1-IF(过程品仓计算!M9="",0,过程品仓计算!M9),0.01)*(1+IF(过程品仓计算!N9="",0,过程品仓计算!N9)),0)</f>
+        <v/>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O9" s="9" t="n"/>
-      <c r="P9" s="10">
-        <f>IFERROR(过程品仓计算!L9+IF(过程品仓计算!M9="",0,过程品仓计算!M9)+IF(过程品仓计算!N9="",0,过程品仓计算!N9)+IF(过程品仓计算!O9="",0,过程品仓计算!O9),0)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P9/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="10">
+        <f>IFERROR(过程品仓计算!L9+IF(过程品仓计算!O9="",0,过程品仓计算!O9)+IF(过程品仓计算!P9="",0,过程品仓计算!P9)+IF(过程品仓计算!Q9="",0,过程品仓计算!Q9),0)</f>
+        <v/>
+      </c>
+      <c r="S9" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R9/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4119,18 +4651,24 @@
         <v/>
       </c>
       <c r="L10" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H10,过程品仓计算!K10),0)</f>
-        <v/>
-      </c>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H10,过程品仓计算!K10)/MAX(1-IF(过程品仓计算!M10="",0,过程品仓计算!M10),0.01)*(1+IF(过程品仓计算!N10="",0,过程品仓计算!N10)),0)</f>
+        <v/>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O10" s="9" t="n"/>
-      <c r="P10" s="10">
-        <f>IFERROR(过程品仓计算!L10+IF(过程品仓计算!M10="",0,过程品仓计算!M10)+IF(过程品仓计算!N10="",0,过程品仓计算!N10)+IF(过程品仓计算!O10="",0,过程品仓计算!O10),0)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P10/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="10">
+        <f>IFERROR(过程品仓计算!L10+IF(过程品仓计算!O10="",0,过程品仓计算!O10)+IF(过程品仓计算!P10="",0,过程品仓计算!P10)+IF(过程品仓计算!Q10="",0,过程品仓计算!Q10),0)</f>
+        <v/>
+      </c>
+      <c r="S10" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R10/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4176,18 +4714,24 @@
         <v/>
       </c>
       <c r="L11" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H11,过程品仓计算!K11),0)</f>
-        <v/>
-      </c>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H11,过程品仓计算!K11)/MAX(1-IF(过程品仓计算!M11="",0,过程品仓计算!M11),0.01)*(1+IF(过程品仓计算!N11="",0,过程品仓计算!N11)),0)</f>
+        <v/>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O11" s="9" t="n"/>
-      <c r="P11" s="10">
-        <f>IFERROR(过程品仓计算!L11+IF(过程品仓计算!M11="",0,过程品仓计算!M11)+IF(过程品仓计算!N11="",0,过程品仓计算!N11)+IF(过程品仓计算!O11="",0,过程品仓计算!O11),0)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P11/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="10">
+        <f>IFERROR(过程品仓计算!L11+IF(过程品仓计算!O11="",0,过程品仓计算!O11)+IF(过程品仓计算!P11="",0,过程品仓计算!P11)+IF(过程品仓计算!Q11="",0,过程品仓计算!Q11),0)</f>
+        <v/>
+      </c>
+      <c r="S11" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R11/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4233,18 +4777,24 @@
         <v/>
       </c>
       <c r="L12" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H12,过程品仓计算!K12),0)</f>
-        <v/>
-      </c>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H12,过程品仓计算!K12)/MAX(1-IF(过程品仓计算!M12="",0,过程品仓计算!M12),0.01)*(1+IF(过程品仓计算!N12="",0,过程品仓计算!N12)),0)</f>
+        <v/>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O12" s="9" t="n"/>
-      <c r="P12" s="10">
-        <f>IFERROR(过程品仓计算!L12+IF(过程品仓计算!M12="",0,过程品仓计算!M12)+IF(过程品仓计算!N12="",0,过程品仓计算!N12)+IF(过程品仓计算!O12="",0,过程品仓计算!O12),0)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P12/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
+      <c r="R12" s="10">
+        <f>IFERROR(过程品仓计算!L12+IF(过程品仓计算!O12="",0,过程品仓计算!O12)+IF(过程品仓计算!P12="",0,过程品仓计算!P12)+IF(过程品仓计算!Q12="",0,过程品仓计算!Q12),0)</f>
+        <v/>
+      </c>
+      <c r="S12" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R12/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4290,18 +4840,24 @@
         <v/>
       </c>
       <c r="L13" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H13,过程品仓计算!K13),0)</f>
-        <v/>
-      </c>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H13,过程品仓计算!K13)/MAX(1-IF(过程品仓计算!M13="",0,过程品仓计算!M13),0.01)*(1+IF(过程品仓计算!N13="",0,过程品仓计算!N13)),0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O13" s="9" t="n"/>
-      <c r="P13" s="10">
-        <f>IFERROR(过程品仓计算!L13+IF(过程品仓计算!M13="",0,过程品仓计算!M13)+IF(过程品仓计算!N13="",0,过程品仓计算!N13)+IF(过程品仓计算!O13="",0,过程品仓计算!O13),0)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P13/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="10">
+        <f>IFERROR(过程品仓计算!L13+IF(过程品仓计算!O13="",0,过程品仓计算!O13)+IF(过程品仓计算!P13="",0,过程品仓计算!P13)+IF(过程品仓计算!Q13="",0,过程品仓计算!Q13),0)</f>
+        <v/>
+      </c>
+      <c r="S13" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R13/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4347,18 +4903,24 @@
         <v/>
       </c>
       <c r="L14" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H14,过程品仓计算!K14),0)</f>
-        <v/>
-      </c>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H14,过程品仓计算!K14)/MAX(1-IF(过程品仓计算!M14="",0,过程品仓计算!M14),0.01)*(1+IF(过程品仓计算!N14="",0,过程品仓计算!N14)),0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O14" s="9" t="n"/>
-      <c r="P14" s="10">
-        <f>IFERROR(过程品仓计算!L14+IF(过程品仓计算!M14="",0,过程品仓计算!M14)+IF(过程品仓计算!N14="",0,过程品仓计算!N14)+IF(过程品仓计算!O14="",0,过程品仓计算!O14),0)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P14/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="9" t="n"/>
+      <c r="R14" s="10">
+        <f>IFERROR(过程品仓计算!L14+IF(过程品仓计算!O14="",0,过程品仓计算!O14)+IF(过程品仓计算!P14="",0,过程品仓计算!P14)+IF(过程品仓计算!Q14="",0,过程品仓计算!Q14),0)</f>
+        <v/>
+      </c>
+      <c r="S14" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R14/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4404,18 +4966,24 @@
         <v/>
       </c>
       <c r="L15" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H15,过程品仓计算!K15),0)</f>
-        <v/>
-      </c>
-      <c r="M15" s="9" t="n"/>
-      <c r="N15" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H15,过程品仓计算!K15)/MAX(1-IF(过程品仓计算!M15="",0,过程品仓计算!M15),0.01)*(1+IF(过程品仓计算!N15="",0,过程品仓计算!N15)),0)</f>
+        <v/>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O15" s="9" t="n"/>
-      <c r="P15" s="10">
-        <f>IFERROR(过程品仓计算!L15+IF(过程品仓计算!M15="",0,过程品仓计算!M15)+IF(过程品仓计算!N15="",0,过程品仓计算!N15)+IF(过程品仓计算!O15="",0,过程品仓计算!O15),0)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P15/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="10">
+        <f>IFERROR(过程品仓计算!L15+IF(过程品仓计算!O15="",0,过程品仓计算!O15)+IF(过程品仓计算!P15="",0,过程品仓计算!P15)+IF(过程品仓计算!Q15="",0,过程品仓计算!Q15),0)</f>
+        <v/>
+      </c>
+      <c r="S15" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R15/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4461,18 +5029,24 @@
         <v/>
       </c>
       <c r="L16" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H16,过程品仓计算!K16),0)</f>
-        <v/>
-      </c>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H16,过程品仓计算!K16)/MAX(1-IF(过程品仓计算!M16="",0,过程品仓计算!M16),0.01)*(1+IF(过程品仓计算!N16="",0,过程品仓计算!N16)),0)</f>
+        <v/>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O16" s="9" t="n"/>
-      <c r="P16" s="10">
-        <f>IFERROR(过程品仓计算!L16+IF(过程品仓计算!M16="",0,过程品仓计算!M16)+IF(过程品仓计算!N16="",0,过程品仓计算!N16)+IF(过程品仓计算!O16="",0,过程品仓计算!O16),0)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P16/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="10">
+        <f>IFERROR(过程品仓计算!L16+IF(过程品仓计算!O16="",0,过程品仓计算!O16)+IF(过程品仓计算!P16="",0,过程品仓计算!P16)+IF(过程品仓计算!Q16="",0,过程品仓计算!Q16),0)</f>
+        <v/>
+      </c>
+      <c r="S16" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R16/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4482,12 +5056,12 @@
           <t>粗破后暂存 小计</t>
         </is>
       </c>
-      <c r="P17" s="10">
-        <f>SUM(P5:P16)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="10">
-        <f>SUM(Q5:Q16)</f>
+      <c r="R17" s="10">
+        <f>SUM(R5:R16)</f>
+        <v/>
+      </c>
+      <c r="S17" s="10">
+        <f>SUM(S5:S16)</f>
         <v/>
       </c>
     </row>
@@ -4540,18 +5114,24 @@
         <v/>
       </c>
       <c r="L19" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H19,过程品仓计算!K19),0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H19,过程品仓计算!K19)/MAX(1-IF(过程品仓计算!M19="",0,过程品仓计算!M19),0.01)*(1+IF(过程品仓计算!N19="",0,过程品仓计算!N19)),0)</f>
+        <v/>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O19" s="9" t="n"/>
-      <c r="P19" s="10">
-        <f>IFERROR(过程品仓计算!L19+IF(过程品仓计算!M19="",0,过程品仓计算!M19)+IF(过程品仓计算!N19="",0,过程品仓计算!N19)+IF(过程品仓计算!O19="",0,过程品仓计算!O19),0)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P19/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="10">
+        <f>IFERROR(过程品仓计算!L19+IF(过程品仓计算!O19="",0,过程品仓计算!O19)+IF(过程品仓计算!P19="",0,过程品仓计算!P19)+IF(过程品仓计算!Q19="",0,过程品仓计算!Q19),0)</f>
+        <v/>
+      </c>
+      <c r="S19" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R19/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4597,18 +5177,24 @@
         <v/>
       </c>
       <c r="L20" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H20,过程品仓计算!K20),0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="9" t="n"/>
-      <c r="N20" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H20,过程品仓计算!K20)/MAX(1-IF(过程品仓计算!M20="",0,过程品仓计算!M20),0.01)*(1+IF(过程品仓计算!N20="",0,过程品仓计算!N20)),0)</f>
+        <v/>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O20" s="9" t="n"/>
-      <c r="P20" s="10">
-        <f>IFERROR(过程品仓计算!L20+IF(过程品仓计算!M20="",0,过程品仓计算!M20)+IF(过程品仓计算!N20="",0,过程品仓计算!N20)+IF(过程品仓计算!O20="",0,过程品仓计算!O20),0)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P20/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="10">
+        <f>IFERROR(过程品仓计算!L20+IF(过程品仓计算!O20="",0,过程品仓计算!O20)+IF(过程品仓计算!P20="",0,过程品仓计算!P20)+IF(过程品仓计算!Q20="",0,过程品仓计算!Q20),0)</f>
+        <v/>
+      </c>
+      <c r="S20" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R20/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4654,18 +5240,24 @@
         <v/>
       </c>
       <c r="L21" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H21,过程品仓计算!K21),0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H21,过程品仓计算!K21)/MAX(1-IF(过程品仓计算!M21="",0,过程品仓计算!M21),0.01)*(1+IF(过程品仓计算!N21="",0,过程品仓计算!N21)),0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O21" s="9" t="n"/>
-      <c r="P21" s="10">
-        <f>IFERROR(过程品仓计算!L21+IF(过程品仓计算!M21="",0,过程品仓计算!M21)+IF(过程品仓计算!N21="",0,过程品仓计算!N21)+IF(过程品仓计算!O21="",0,过程品仓计算!O21),0)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P21/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="10">
+        <f>IFERROR(过程品仓计算!L21+IF(过程品仓计算!O21="",0,过程品仓计算!O21)+IF(过程品仓计算!P21="",0,过程品仓计算!P21)+IF(过程品仓计算!Q21="",0,过程品仓计算!Q21),0)</f>
+        <v/>
+      </c>
+      <c r="S21" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R21/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4711,18 +5303,24 @@
         <v/>
       </c>
       <c r="L22" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H22,过程品仓计算!K22),0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H22,过程品仓计算!K22)/MAX(1-IF(过程品仓计算!M22="",0,过程品仓计算!M22),0.01)*(1+IF(过程品仓计算!N22="",0,过程品仓计算!N22)),0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O22" s="9" t="n"/>
-      <c r="P22" s="10">
-        <f>IFERROR(过程品仓计算!L22+IF(过程品仓计算!M22="",0,过程品仓计算!M22)+IF(过程品仓计算!N22="",0,过程品仓计算!N22)+IF(过程品仓计算!O22="",0,过程品仓计算!O22),0)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P22/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="10">
+        <f>IFERROR(过程品仓计算!L22+IF(过程品仓计算!O22="",0,过程品仓计算!O22)+IF(过程品仓计算!P22="",0,过程品仓计算!P22)+IF(过程品仓计算!Q22="",0,过程品仓计算!Q22),0)</f>
+        <v/>
+      </c>
+      <c r="S22" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R22/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4768,18 +5366,24 @@
         <v/>
       </c>
       <c r="L23" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H23,过程品仓计算!K23),0)</f>
-        <v/>
-      </c>
-      <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H23,过程品仓计算!K23)/MAX(1-IF(过程品仓计算!M23="",0,过程品仓计算!M23),0.01)*(1+IF(过程品仓计算!N23="",0,过程品仓计算!N23)),0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O23" s="9" t="n"/>
-      <c r="P23" s="10">
-        <f>IFERROR(过程品仓计算!L23+IF(过程品仓计算!M23="",0,过程品仓计算!M23)+IF(过程品仓计算!N23="",0,过程品仓计算!N23)+IF(过程品仓计算!O23="",0,过程品仓计算!O23),0)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P23/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="10">
+        <f>IFERROR(过程品仓计算!L23+IF(过程品仓计算!O23="",0,过程品仓计算!O23)+IF(过程品仓计算!P23="",0,过程品仓计算!P23)+IF(过程品仓计算!Q23="",0,过程品仓计算!Q23),0)</f>
+        <v/>
+      </c>
+      <c r="S23" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R23/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4825,18 +5429,24 @@
         <v/>
       </c>
       <c r="L24" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H24,过程品仓计算!K24),0)</f>
-        <v/>
-      </c>
-      <c r="M24" s="9" t="n"/>
-      <c r="N24" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H24,过程品仓计算!K24)/MAX(1-IF(过程品仓计算!M24="",0,过程品仓计算!M24),0.01)*(1+IF(过程品仓计算!N24="",0,过程品仓计算!N24)),0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O24" s="9" t="n"/>
-      <c r="P24" s="10">
-        <f>IFERROR(过程品仓计算!L24+IF(过程品仓计算!M24="",0,过程品仓计算!M24)+IF(过程品仓计算!N24="",0,过程品仓计算!N24)+IF(过程品仓计算!O24="",0,过程品仓计算!O24),0)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P24/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="10">
+        <f>IFERROR(过程品仓计算!L24+IF(过程品仓计算!O24="",0,过程品仓计算!O24)+IF(过程品仓计算!P24="",0,过程品仓计算!P24)+IF(过程品仓计算!Q24="",0,过程品仓计算!Q24),0)</f>
+        <v/>
+      </c>
+      <c r="S24" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R24/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4882,18 +5492,24 @@
         <v/>
       </c>
       <c r="L25" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H25,过程品仓计算!K25),0)</f>
-        <v/>
-      </c>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H25,过程品仓计算!K25)/MAX(1-IF(过程品仓计算!M25="",0,过程品仓计算!M25),0.01)*(1+IF(过程品仓计算!N25="",0,过程品仓计算!N25)),0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O25" s="9" t="n"/>
-      <c r="P25" s="10">
-        <f>IFERROR(过程品仓计算!L25+IF(过程品仓计算!M25="",0,过程品仓计算!M25)+IF(过程品仓计算!N25="",0,过程品仓计算!N25)+IF(过程品仓计算!O25="",0,过程品仓计算!O25),0)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P25/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="10">
+        <f>IFERROR(过程品仓计算!L25+IF(过程品仓计算!O25="",0,过程品仓计算!O25)+IF(过程品仓计算!P25="",0,过程品仓计算!P25)+IF(过程品仓计算!Q25="",0,过程品仓计算!Q25),0)</f>
+        <v/>
+      </c>
+      <c r="S25" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R25/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4939,18 +5555,24 @@
         <v/>
       </c>
       <c r="L26" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H26,过程品仓计算!K26),0)</f>
-        <v/>
-      </c>
-      <c r="M26" s="9" t="n"/>
-      <c r="N26" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H26,过程品仓计算!K26)/MAX(1-IF(过程品仓计算!M26="",0,过程品仓计算!M26),0.01)*(1+IF(过程品仓计算!N26="",0,过程品仓计算!N26)),0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O26" s="9" t="n"/>
-      <c r="P26" s="10">
-        <f>IFERROR(过程品仓计算!L26+IF(过程品仓计算!M26="",0,过程品仓计算!M26)+IF(过程品仓计算!N26="",0,过程品仓计算!N26)+IF(过程品仓计算!O26="",0,过程品仓计算!O26),0)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P26/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="10">
+        <f>IFERROR(过程品仓计算!L26+IF(过程品仓计算!O26="",0,过程品仓计算!O26)+IF(过程品仓计算!P26="",0,过程品仓计算!P26)+IF(过程品仓计算!Q26="",0,过程品仓计算!Q26),0)</f>
+        <v/>
+      </c>
+      <c r="S26" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R26/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -4996,18 +5618,24 @@
         <v/>
       </c>
       <c r="L27" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H27,过程品仓计算!K27),0)</f>
-        <v/>
-      </c>
-      <c r="M27" s="9" t="n"/>
-      <c r="N27" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H27,过程品仓计算!K27)/MAX(1-IF(过程品仓计算!M27="",0,过程品仓计算!M27),0.01)*(1+IF(过程品仓计算!N27="",0,过程品仓计算!N27)),0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O27" s="9" t="n"/>
-      <c r="P27" s="10">
-        <f>IFERROR(过程品仓计算!L27+IF(过程品仓计算!M27="",0,过程品仓计算!M27)+IF(过程品仓计算!N27="",0,过程品仓计算!N27)+IF(过程品仓计算!O27="",0,过程品仓计算!O27),0)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P27/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="10">
+        <f>IFERROR(过程品仓计算!L27+IF(过程品仓计算!O27="",0,过程品仓计算!O27)+IF(过程品仓计算!P27="",0,过程品仓计算!P27)+IF(过程品仓计算!Q27="",0,过程品仓计算!Q27),0)</f>
+        <v/>
+      </c>
+      <c r="S27" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R27/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5053,18 +5681,24 @@
         <v/>
       </c>
       <c r="L28" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H28,过程品仓计算!K28),0)</f>
-        <v/>
-      </c>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H28,过程品仓计算!K28)/MAX(1-IF(过程品仓计算!M28="",0,过程品仓计算!M28),0.01)*(1+IF(过程品仓计算!N28="",0,过程品仓计算!N28)),0)</f>
+        <v/>
+      </c>
+      <c r="M28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O28" s="9" t="n"/>
-      <c r="P28" s="10">
-        <f>IFERROR(过程品仓计算!L28+IF(过程品仓计算!M28="",0,过程品仓计算!M28)+IF(过程品仓计算!N28="",0,过程品仓计算!N28)+IF(过程品仓计算!O28="",0,过程品仓计算!O28),0)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P28/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P28" s="9" t="n"/>
+      <c r="Q28" s="9" t="n"/>
+      <c r="R28" s="10">
+        <f>IFERROR(过程品仓计算!L28+IF(过程品仓计算!O28="",0,过程品仓计算!O28)+IF(过程品仓计算!P28="",0,过程品仓计算!P28)+IF(过程品仓计算!Q28="",0,过程品仓计算!Q28),0)</f>
+        <v/>
+      </c>
+      <c r="S28" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R28/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5110,18 +5744,24 @@
         <v/>
       </c>
       <c r="L29" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H29,过程品仓计算!K29),0)</f>
-        <v/>
-      </c>
-      <c r="M29" s="9" t="n"/>
-      <c r="N29" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H29,过程品仓计算!K29)/MAX(1-IF(过程品仓计算!M29="",0,过程品仓计算!M29),0.01)*(1+IF(过程品仓计算!N29="",0,过程品仓计算!N29)),0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O29" s="9" t="n"/>
-      <c r="P29" s="10">
-        <f>IFERROR(过程品仓计算!L29+IF(过程品仓计算!M29="",0,过程品仓计算!M29)+IF(过程品仓计算!N29="",0,过程品仓计算!N29)+IF(过程品仓计算!O29="",0,过程品仓计算!O29),0)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P29/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+      <c r="R29" s="10">
+        <f>IFERROR(过程品仓计算!L29+IF(过程品仓计算!O29="",0,过程品仓计算!O29)+IF(过程品仓计算!P29="",0,过程品仓计算!P29)+IF(过程品仓计算!Q29="",0,过程品仓计算!Q29),0)</f>
+        <v/>
+      </c>
+      <c r="S29" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R29/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5167,18 +5807,24 @@
         <v/>
       </c>
       <c r="L30" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H30,过程品仓计算!K30),0)</f>
-        <v/>
-      </c>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H30,过程品仓计算!K30)/MAX(1-IF(过程品仓计算!M30="",0,过程品仓计算!M30),0.01)*(1+IF(过程品仓计算!N30="",0,过程品仓计算!N30)),0)</f>
+        <v/>
+      </c>
+      <c r="M30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O30" s="9" t="n"/>
-      <c r="P30" s="10">
-        <f>IFERROR(过程品仓计算!L30+IF(过程品仓计算!M30="",0,过程品仓计算!M30)+IF(过程品仓计算!N30="",0,过程品仓计算!N30)+IF(过程品仓计算!O30="",0,过程品仓计算!O30),0)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P30/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P30" s="9" t="n"/>
+      <c r="Q30" s="9" t="n"/>
+      <c r="R30" s="10">
+        <f>IFERROR(过程品仓计算!L30+IF(过程品仓计算!O30="",0,过程品仓计算!O30)+IF(过程品仓计算!P30="",0,过程品仓计算!P30)+IF(过程品仓计算!Q30="",0,过程品仓计算!Q30),0)</f>
+        <v/>
+      </c>
+      <c r="S30" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R30/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5188,12 +5834,12 @@
           <t>烘干后暂存 小计</t>
         </is>
       </c>
-      <c r="P31" s="10">
-        <f>SUM(P19:P30)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="10">
-        <f>SUM(Q19:Q30)</f>
+      <c r="R31" s="10">
+        <f>SUM(R19:R30)</f>
+        <v/>
+      </c>
+      <c r="S31" s="10">
+        <f>SUM(S19:S30)</f>
         <v/>
       </c>
     </row>
@@ -5246,18 +5892,24 @@
         <v/>
       </c>
       <c r="L33" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H33,过程品仓计算!K33),0)</f>
-        <v/>
-      </c>
-      <c r="M33" s="9" t="n"/>
-      <c r="N33" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H33,过程品仓计算!K33)/MAX(1-IF(过程品仓计算!M33="",0,过程品仓计算!M33),0.01)*(1+IF(过程品仓计算!N33="",0,过程品仓计算!N33)),0)</f>
+        <v/>
+      </c>
+      <c r="M33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O33" s="9" t="n"/>
-      <c r="P33" s="10">
-        <f>IFERROR(过程品仓计算!L33+IF(过程品仓计算!M33="",0,过程品仓计算!M33)+IF(过程品仓计算!N33="",0,过程品仓计算!N33)+IF(过程品仓计算!O33="",0,过程品仓计算!O33),0)</f>
-        <v/>
-      </c>
-      <c r="Q33" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P33/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P33" s="9" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="10">
+        <f>IFERROR(过程品仓计算!L33+IF(过程品仓计算!O33="",0,过程品仓计算!O33)+IF(过程品仓计算!P33="",0,过程品仓计算!P33)+IF(过程品仓计算!Q33="",0,过程品仓计算!Q33),0)</f>
+        <v/>
+      </c>
+      <c r="S33" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R33/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5303,18 +5955,24 @@
         <v/>
       </c>
       <c r="L34" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H34,过程品仓计算!K34),0)</f>
-        <v/>
-      </c>
-      <c r="M34" s="9" t="n"/>
-      <c r="N34" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H34,过程品仓计算!K34)/MAX(1-IF(过程品仓计算!M34="",0,过程品仓计算!M34),0.01)*(1+IF(过程品仓计算!N34="",0,过程品仓计算!N34)),0)</f>
+        <v/>
+      </c>
+      <c r="M34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O34" s="9" t="n"/>
-      <c r="P34" s="10">
-        <f>IFERROR(过程品仓计算!L34+IF(过程品仓计算!M34="",0,过程品仓计算!M34)+IF(过程品仓计算!N34="",0,过程品仓计算!N34)+IF(过程品仓计算!O34="",0,过程品仓计算!O34),0)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P34/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="10">
+        <f>IFERROR(过程品仓计算!L34+IF(过程品仓计算!O34="",0,过程品仓计算!O34)+IF(过程品仓计算!P34="",0,过程品仓计算!P34)+IF(过程品仓计算!Q34="",0,过程品仓计算!Q34),0)</f>
+        <v/>
+      </c>
+      <c r="S34" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R34/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5360,18 +6018,24 @@
         <v/>
       </c>
       <c r="L35" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H35,过程品仓计算!K35),0)</f>
-        <v/>
-      </c>
-      <c r="M35" s="9" t="n"/>
-      <c r="N35" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H35,过程品仓计算!K35)/MAX(1-IF(过程品仓计算!M35="",0,过程品仓计算!M35),0.01)*(1+IF(过程品仓计算!N35="",0,过程品仓计算!N35)),0)</f>
+        <v/>
+      </c>
+      <c r="M35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O35" s="9" t="n"/>
-      <c r="P35" s="10">
-        <f>IFERROR(过程品仓计算!L35+IF(过程品仓计算!M35="",0,过程品仓计算!M35)+IF(过程品仓计算!N35="",0,过程品仓计算!N35)+IF(过程品仓计算!O35="",0,过程品仓计算!O35),0)</f>
-        <v/>
-      </c>
-      <c r="Q35" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P35/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="10">
+        <f>IFERROR(过程品仓计算!L35+IF(过程品仓计算!O35="",0,过程品仓计算!O35)+IF(过程品仓计算!P35="",0,过程品仓计算!P35)+IF(过程品仓计算!Q35="",0,过程品仓计算!Q35),0)</f>
+        <v/>
+      </c>
+      <c r="S35" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R35/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5417,18 +6081,24 @@
         <v/>
       </c>
       <c r="L36" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H36,过程品仓计算!K36),0)</f>
-        <v/>
-      </c>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H36,过程品仓计算!K36)/MAX(1-IF(过程品仓计算!M36="",0,过程品仓计算!M36),0.01)*(1+IF(过程品仓计算!N36="",0,过程品仓计算!N36)),0)</f>
+        <v/>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O36" s="9" t="n"/>
-      <c r="P36" s="10">
-        <f>IFERROR(过程品仓计算!L36+IF(过程品仓计算!M36="",0,过程品仓计算!M36)+IF(过程品仓计算!N36="",0,过程品仓计算!N36)+IF(过程品仓计算!O36="",0,过程品仓计算!O36),0)</f>
-        <v/>
-      </c>
-      <c r="Q36" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P36/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P36" s="9" t="n"/>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="10">
+        <f>IFERROR(过程品仓计算!L36+IF(过程品仓计算!O36="",0,过程品仓计算!O36)+IF(过程品仓计算!P36="",0,过程品仓计算!P36)+IF(过程品仓计算!Q36="",0,过程品仓计算!Q36),0)</f>
+        <v/>
+      </c>
+      <c r="S36" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R36/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5474,18 +6144,24 @@
         <v/>
       </c>
       <c r="L37" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H37,过程品仓计算!K37),0)</f>
-        <v/>
-      </c>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H37,过程品仓计算!K37)/MAX(1-IF(过程品仓计算!M37="",0,过程品仓计算!M37),0.01)*(1+IF(过程品仓计算!N37="",0,过程品仓计算!N37)),0)</f>
+        <v/>
+      </c>
+      <c r="M37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O37" s="9" t="n"/>
-      <c r="P37" s="10">
-        <f>IFERROR(过程品仓计算!L37+IF(过程品仓计算!M37="",0,过程品仓计算!M37)+IF(过程品仓计算!N37="",0,过程品仓计算!N37)+IF(过程品仓计算!O37="",0,过程品仓计算!O37),0)</f>
-        <v/>
-      </c>
-      <c r="Q37" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P37/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P37" s="9" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="10">
+        <f>IFERROR(过程品仓计算!L37+IF(过程品仓计算!O37="",0,过程品仓计算!O37)+IF(过程品仓计算!P37="",0,过程品仓计算!P37)+IF(过程品仓计算!Q37="",0,过程品仓计算!Q37),0)</f>
+        <v/>
+      </c>
+      <c r="S37" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R37/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5531,18 +6207,24 @@
         <v/>
       </c>
       <c r="L38" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H38,过程品仓计算!K38),0)</f>
-        <v/>
-      </c>
-      <c r="M38" s="9" t="n"/>
-      <c r="N38" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H38,过程品仓计算!K38)/MAX(1-IF(过程品仓计算!M38="",0,过程品仓计算!M38),0.01)*(1+IF(过程品仓计算!N38="",0,过程品仓计算!N38)),0)</f>
+        <v/>
+      </c>
+      <c r="M38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O38" s="9" t="n"/>
-      <c r="P38" s="10">
-        <f>IFERROR(过程品仓计算!L38+IF(过程品仓计算!M38="",0,过程品仓计算!M38)+IF(过程品仓计算!N38="",0,过程品仓计算!N38)+IF(过程品仓计算!O38="",0,过程品仓计算!O38),0)</f>
-        <v/>
-      </c>
-      <c r="Q38" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P38/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P38" s="9" t="n"/>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="10">
+        <f>IFERROR(过程品仓计算!L38+IF(过程品仓计算!O38="",0,过程品仓计算!O38)+IF(过程品仓计算!P38="",0,过程品仓计算!P38)+IF(过程品仓计算!Q38="",0,过程品仓计算!Q38),0)</f>
+        <v/>
+      </c>
+      <c r="S38" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R38/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5588,18 +6270,24 @@
         <v/>
       </c>
       <c r="L39" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H39,过程品仓计算!K39),0)</f>
-        <v/>
-      </c>
-      <c r="M39" s="9" t="n"/>
-      <c r="N39" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H39,过程品仓计算!K39)/MAX(1-IF(过程品仓计算!M39="",0,过程品仓计算!M39),0.01)*(1+IF(过程品仓计算!N39="",0,过程品仓计算!N39)),0)</f>
+        <v/>
+      </c>
+      <c r="M39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O39" s="9" t="n"/>
-      <c r="P39" s="10">
-        <f>IFERROR(过程品仓计算!L39+IF(过程品仓计算!M39="",0,过程品仓计算!M39)+IF(过程品仓计算!N39="",0,过程品仓计算!N39)+IF(过程品仓计算!O39="",0,过程品仓计算!O39),0)</f>
-        <v/>
-      </c>
-      <c r="Q39" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P39/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P39" s="9" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="10">
+        <f>IFERROR(过程品仓计算!L39+IF(过程品仓计算!O39="",0,过程品仓计算!O39)+IF(过程品仓计算!P39="",0,过程品仓计算!P39)+IF(过程品仓计算!Q39="",0,过程品仓计算!Q39),0)</f>
+        <v/>
+      </c>
+      <c r="S39" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R39/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5645,18 +6333,24 @@
         <v/>
       </c>
       <c r="L40" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H40,过程品仓计算!K40),0)</f>
-        <v/>
-      </c>
-      <c r="M40" s="9" t="n"/>
-      <c r="N40" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H40,过程品仓计算!K40)/MAX(1-IF(过程品仓计算!M40="",0,过程品仓计算!M40),0.01)*(1+IF(过程品仓计算!N40="",0,过程品仓计算!N40)),0)</f>
+        <v/>
+      </c>
+      <c r="M40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O40" s="9" t="n"/>
-      <c r="P40" s="10">
-        <f>IFERROR(过程品仓计算!L40+IF(过程品仓计算!M40="",0,过程品仓计算!M40)+IF(过程品仓计算!N40="",0,过程品仓计算!N40)+IF(过程品仓计算!O40="",0,过程品仓计算!O40),0)</f>
-        <v/>
-      </c>
-      <c r="Q40" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P40/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P40" s="9" t="n"/>
+      <c r="Q40" s="9" t="n"/>
+      <c r="R40" s="10">
+        <f>IFERROR(过程品仓计算!L40+IF(过程品仓计算!O40="",0,过程品仓计算!O40)+IF(过程品仓计算!P40="",0,过程品仓计算!P40)+IF(过程品仓计算!Q40="",0,过程品仓计算!Q40),0)</f>
+        <v/>
+      </c>
+      <c r="S40" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R40/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5702,18 +6396,24 @@
         <v/>
       </c>
       <c r="L41" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H41,过程品仓计算!K41),0)</f>
-        <v/>
-      </c>
-      <c r="M41" s="9" t="n"/>
-      <c r="N41" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H41,过程品仓计算!K41)/MAX(1-IF(过程品仓计算!M41="",0,过程品仓计算!M41),0.01)*(1+IF(过程品仓计算!N41="",0,过程品仓计算!N41)),0)</f>
+        <v/>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O41" s="9" t="n"/>
-      <c r="P41" s="10">
-        <f>IFERROR(过程品仓计算!L41+IF(过程品仓计算!M41="",0,过程品仓计算!M41)+IF(过程品仓计算!N41="",0,过程品仓计算!N41)+IF(过程品仓计算!O41="",0,过程品仓计算!O41),0)</f>
-        <v/>
-      </c>
-      <c r="Q41" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P41/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P41" s="9" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="10">
+        <f>IFERROR(过程品仓计算!L41+IF(过程品仓计算!O41="",0,过程品仓计算!O41)+IF(过程品仓计算!P41="",0,过程品仓计算!P41)+IF(过程品仓计算!Q41="",0,过程品仓计算!Q41),0)</f>
+        <v/>
+      </c>
+      <c r="S41" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R41/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5759,18 +6459,24 @@
         <v/>
       </c>
       <c r="L42" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H42,过程品仓计算!K42),0)</f>
-        <v/>
-      </c>
-      <c r="M42" s="9" t="n"/>
-      <c r="N42" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H42,过程品仓计算!K42)/MAX(1-IF(过程品仓计算!M42="",0,过程品仓计算!M42),0.01)*(1+IF(过程品仓计算!N42="",0,过程品仓计算!N42)),0)</f>
+        <v/>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O42" s="9" t="n"/>
-      <c r="P42" s="10">
-        <f>IFERROR(过程品仓计算!L42+IF(过程品仓计算!M42="",0,过程品仓计算!M42)+IF(过程品仓计算!N42="",0,过程品仓计算!N42)+IF(过程品仓计算!O42="",0,过程品仓计算!O42),0)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P42/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P42" s="9" t="n"/>
+      <c r="Q42" s="9" t="n"/>
+      <c r="R42" s="10">
+        <f>IFERROR(过程品仓计算!L42+IF(过程品仓计算!O42="",0,过程品仓计算!O42)+IF(过程品仓计算!P42="",0,过程品仓计算!P42)+IF(过程品仓计算!Q42="",0,过程品仓计算!Q42),0)</f>
+        <v/>
+      </c>
+      <c r="S42" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R42/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5816,18 +6522,24 @@
         <v/>
       </c>
       <c r="L43" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H43,过程品仓计算!K43),0)</f>
-        <v/>
-      </c>
-      <c r="M43" s="9" t="n"/>
-      <c r="N43" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H43,过程品仓计算!K43)/MAX(1-IF(过程品仓计算!M43="",0,过程品仓计算!M43),0.01)*(1+IF(过程品仓计算!N43="",0,过程品仓计算!N43)),0)</f>
+        <v/>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O43" s="9" t="n"/>
-      <c r="P43" s="10">
-        <f>IFERROR(过程品仓计算!L43+IF(过程品仓计算!M43="",0,过程品仓计算!M43)+IF(过程品仓计算!N43="",0,过程品仓计算!N43)+IF(过程品仓计算!O43="",0,过程品仓计算!O43),0)</f>
-        <v/>
-      </c>
-      <c r="Q43" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P43/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P43" s="9" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="10">
+        <f>IFERROR(过程品仓计算!L43+IF(过程品仓计算!O43="",0,过程品仓计算!O43)+IF(过程品仓计算!P43="",0,过程品仓计算!P43)+IF(过程品仓计算!Q43="",0,过程品仓计算!Q43),0)</f>
+        <v/>
+      </c>
+      <c r="S43" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R43/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5873,18 +6585,24 @@
         <v/>
       </c>
       <c r="L44" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H44,过程品仓计算!K44),0)</f>
-        <v/>
-      </c>
-      <c r="M44" s="9" t="n"/>
-      <c r="N44" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H44,过程品仓计算!K44)/MAX(1-IF(过程品仓计算!M44="",0,过程品仓计算!M44),0.01)*(1+IF(过程品仓计算!N44="",0,过程品仓计算!N44)),0)</f>
+        <v/>
+      </c>
+      <c r="M44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O44" s="9" t="n"/>
-      <c r="P44" s="10">
-        <f>IFERROR(过程品仓计算!L44+IF(过程品仓计算!M44="",0,过程品仓计算!M44)+IF(过程品仓计算!N44="",0,过程品仓计算!N44)+IF(过程品仓计算!O44="",0,过程品仓计算!O44),0)</f>
-        <v/>
-      </c>
-      <c r="Q44" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P44/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P44" s="9" t="n"/>
+      <c r="Q44" s="9" t="n"/>
+      <c r="R44" s="10">
+        <f>IFERROR(过程品仓计算!L44+IF(过程品仓计算!O44="",0,过程品仓计算!O44)+IF(过程品仓计算!P44="",0,过程品仓计算!P44)+IF(过程品仓计算!Q44="",0,过程品仓计算!Q44),0)</f>
+        <v/>
+      </c>
+      <c r="S44" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R44/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -5894,12 +6612,12 @@
           <t>磨粉后暂存 小计</t>
         </is>
       </c>
-      <c r="P45" s="10">
-        <f>SUM(P33:P44)</f>
-        <v/>
-      </c>
-      <c r="Q45" s="10">
-        <f>SUM(Q33:Q44)</f>
+      <c r="R45" s="10">
+        <f>SUM(R33:R44)</f>
+        <v/>
+      </c>
+      <c r="S45" s="10">
+        <f>SUM(S33:S44)</f>
         <v/>
       </c>
     </row>
@@ -5952,18 +6670,24 @@
         <v/>
       </c>
       <c r="L47" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H47,过程品仓计算!K47),0)</f>
-        <v/>
-      </c>
-      <c r="M47" s="9" t="n"/>
-      <c r="N47" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H47,过程品仓计算!K47)/MAX(1-IF(过程品仓计算!M47="",0,过程品仓计算!M47),0.01)*(1+IF(过程品仓计算!N47="",0,过程品仓计算!N47)),0)</f>
+        <v/>
+      </c>
+      <c r="M47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O47" s="9" t="n"/>
-      <c r="P47" s="10">
-        <f>IFERROR(过程品仓计算!L47+IF(过程品仓计算!M47="",0,过程品仓计算!M47)+IF(过程品仓计算!N47="",0,过程品仓计算!N47)+IF(过程品仓计算!O47="",0,过程品仓计算!O47),0)</f>
-        <v/>
-      </c>
-      <c r="Q47" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P47/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="10">
+        <f>IFERROR(过程品仓计算!L47+IF(过程品仓计算!O47="",0,过程品仓计算!O47)+IF(过程品仓计算!P47="",0,过程品仓计算!P47)+IF(过程品仓计算!Q47="",0,过程品仓计算!Q47),0)</f>
+        <v/>
+      </c>
+      <c r="S47" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R47/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6009,18 +6733,24 @@
         <v/>
       </c>
       <c r="L48" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H48,过程品仓计算!K48),0)</f>
-        <v/>
-      </c>
-      <c r="M48" s="9" t="n"/>
-      <c r="N48" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H48,过程品仓计算!K48)/MAX(1-IF(过程品仓计算!M48="",0,过程品仓计算!M48),0.01)*(1+IF(过程品仓计算!N48="",0,过程品仓计算!N48)),0)</f>
+        <v/>
+      </c>
+      <c r="M48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O48" s="9" t="n"/>
-      <c r="P48" s="10">
-        <f>IFERROR(过程品仓计算!L48+IF(过程品仓计算!M48="",0,过程品仓计算!M48)+IF(过程品仓计算!N48="",0,过程品仓计算!N48)+IF(过程品仓计算!O48="",0,过程品仓计算!O48),0)</f>
-        <v/>
-      </c>
-      <c r="Q48" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P48/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P48" s="9" t="n"/>
+      <c r="Q48" s="9" t="n"/>
+      <c r="R48" s="10">
+        <f>IFERROR(过程品仓计算!L48+IF(过程品仓计算!O48="",0,过程品仓计算!O48)+IF(过程品仓计算!P48="",0,过程品仓计算!P48)+IF(过程品仓计算!Q48="",0,过程品仓计算!Q48),0)</f>
+        <v/>
+      </c>
+      <c r="S48" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R48/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6066,18 +6796,24 @@
         <v/>
       </c>
       <c r="L49" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H49,过程品仓计算!K49),0)</f>
-        <v/>
-      </c>
-      <c r="M49" s="9" t="n"/>
-      <c r="N49" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H49,过程品仓计算!K49)/MAX(1-IF(过程品仓计算!M49="",0,过程品仓计算!M49),0.01)*(1+IF(过程品仓计算!N49="",0,过程品仓计算!N49)),0)</f>
+        <v/>
+      </c>
+      <c r="M49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O49" s="9" t="n"/>
-      <c r="P49" s="10">
-        <f>IFERROR(过程品仓计算!L49+IF(过程品仓计算!M49="",0,过程品仓计算!M49)+IF(过程品仓计算!N49="",0,过程品仓计算!N49)+IF(过程品仓计算!O49="",0,过程品仓计算!O49),0)</f>
-        <v/>
-      </c>
-      <c r="Q49" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P49/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P49" s="9" t="n"/>
+      <c r="Q49" s="9" t="n"/>
+      <c r="R49" s="10">
+        <f>IFERROR(过程品仓计算!L49+IF(过程品仓计算!O49="",0,过程品仓计算!O49)+IF(过程品仓计算!P49="",0,过程品仓计算!P49)+IF(过程品仓计算!Q49="",0,过程品仓计算!Q49),0)</f>
+        <v/>
+      </c>
+      <c r="S49" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R49/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6123,18 +6859,24 @@
         <v/>
       </c>
       <c r="L50" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H50,过程品仓计算!K50),0)</f>
-        <v/>
-      </c>
-      <c r="M50" s="9" t="n"/>
-      <c r="N50" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H50,过程品仓计算!K50)/MAX(1-IF(过程品仓计算!M50="",0,过程品仓计算!M50),0.01)*(1+IF(过程品仓计算!N50="",0,过程品仓计算!N50)),0)</f>
+        <v/>
+      </c>
+      <c r="M50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O50" s="9" t="n"/>
-      <c r="P50" s="10">
-        <f>IFERROR(过程品仓计算!L50+IF(过程品仓计算!M50="",0,过程品仓计算!M50)+IF(过程品仓计算!N50="",0,过程品仓计算!N50)+IF(过程品仓计算!O50="",0,过程品仓计算!O50),0)</f>
-        <v/>
-      </c>
-      <c r="Q50" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P50/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P50" s="9" t="n"/>
+      <c r="Q50" s="9" t="n"/>
+      <c r="R50" s="10">
+        <f>IFERROR(过程品仓计算!L50+IF(过程品仓计算!O50="",0,过程品仓计算!O50)+IF(过程品仓计算!P50="",0,过程品仓计算!P50)+IF(过程品仓计算!Q50="",0,过程品仓计算!Q50),0)</f>
+        <v/>
+      </c>
+      <c r="S50" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R50/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6180,18 +6922,24 @@
         <v/>
       </c>
       <c r="L51" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H51,过程品仓计算!K51),0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="9" t="n"/>
-      <c r="N51" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H51,过程品仓计算!K51)/MAX(1-IF(过程品仓计算!M51="",0,过程品仓计算!M51),0.01)*(1+IF(过程品仓计算!N51="",0,过程品仓计算!N51)),0)</f>
+        <v/>
+      </c>
+      <c r="M51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O51" s="9" t="n"/>
-      <c r="P51" s="10">
-        <f>IFERROR(过程品仓计算!L51+IF(过程品仓计算!M51="",0,过程品仓计算!M51)+IF(过程品仓计算!N51="",0,过程品仓计算!N51)+IF(过程品仓计算!O51="",0,过程品仓计算!O51),0)</f>
-        <v/>
-      </c>
-      <c r="Q51" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P51/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P51" s="9" t="n"/>
+      <c r="Q51" s="9" t="n"/>
+      <c r="R51" s="10">
+        <f>IFERROR(过程品仓计算!L51+IF(过程品仓计算!O51="",0,过程品仓计算!O51)+IF(过程品仓计算!P51="",0,过程品仓计算!P51)+IF(过程品仓计算!Q51="",0,过程品仓计算!Q51),0)</f>
+        <v/>
+      </c>
+      <c r="S51" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R51/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6237,18 +6985,24 @@
         <v/>
       </c>
       <c r="L52" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H52,过程品仓计算!K52),0)</f>
-        <v/>
-      </c>
-      <c r="M52" s="9" t="n"/>
-      <c r="N52" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H52,过程品仓计算!K52)/MAX(1-IF(过程品仓计算!M52="",0,过程品仓计算!M52),0.01)*(1+IF(过程品仓计算!N52="",0,过程品仓计算!N52)),0)</f>
+        <v/>
+      </c>
+      <c r="M52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O52" s="9" t="n"/>
-      <c r="P52" s="10">
-        <f>IFERROR(过程品仓计算!L52+IF(过程品仓计算!M52="",0,过程品仓计算!M52)+IF(过程品仓计算!N52="",0,过程品仓计算!N52)+IF(过程品仓计算!O52="",0,过程品仓计算!O52),0)</f>
-        <v/>
-      </c>
-      <c r="Q52" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P52/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P52" s="9" t="n"/>
+      <c r="Q52" s="9" t="n"/>
+      <c r="R52" s="10">
+        <f>IFERROR(过程品仓计算!L52+IF(过程品仓计算!O52="",0,过程品仓计算!O52)+IF(过程品仓计算!P52="",0,过程品仓计算!P52)+IF(过程品仓计算!Q52="",0,过程品仓计算!Q52),0)</f>
+        <v/>
+      </c>
+      <c r="S52" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R52/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6294,18 +7048,24 @@
         <v/>
       </c>
       <c r="L53" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H53,过程品仓计算!K53),0)</f>
-        <v/>
-      </c>
-      <c r="M53" s="9" t="n"/>
-      <c r="N53" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H53,过程品仓计算!K53)/MAX(1-IF(过程品仓计算!M53="",0,过程品仓计算!M53),0.01)*(1+IF(过程品仓计算!N53="",0,过程品仓计算!N53)),0)</f>
+        <v/>
+      </c>
+      <c r="M53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O53" s="9" t="n"/>
-      <c r="P53" s="10">
-        <f>IFERROR(过程品仓计算!L53+IF(过程品仓计算!M53="",0,过程品仓计算!M53)+IF(过程品仓计算!N53="",0,过程品仓计算!N53)+IF(过程品仓计算!O53="",0,过程品仓计算!O53),0)</f>
-        <v/>
-      </c>
-      <c r="Q53" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P53/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="9" t="n"/>
+      <c r="R53" s="10">
+        <f>IFERROR(过程品仓计算!L53+IF(过程品仓计算!O53="",0,过程品仓计算!O53)+IF(过程品仓计算!P53="",0,过程品仓计算!P53)+IF(过程品仓计算!Q53="",0,过程品仓计算!Q53),0)</f>
+        <v/>
+      </c>
+      <c r="S53" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R53/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6351,18 +7111,24 @@
         <v/>
       </c>
       <c r="L54" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H54,过程品仓计算!K54),0)</f>
-        <v/>
-      </c>
-      <c r="M54" s="9" t="n"/>
-      <c r="N54" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H54,过程品仓计算!K54)/MAX(1-IF(过程品仓计算!M54="",0,过程品仓计算!M54),0.01)*(1+IF(过程品仓计算!N54="",0,过程品仓计算!N54)),0)</f>
+        <v/>
+      </c>
+      <c r="M54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O54" s="9" t="n"/>
-      <c r="P54" s="10">
-        <f>IFERROR(过程品仓计算!L54+IF(过程品仓计算!M54="",0,过程品仓计算!M54)+IF(过程品仓计算!N54="",0,过程品仓计算!N54)+IF(过程品仓计算!O54="",0,过程品仓计算!O54),0)</f>
-        <v/>
-      </c>
-      <c r="Q54" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P54/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P54" s="9" t="n"/>
+      <c r="Q54" s="9" t="n"/>
+      <c r="R54" s="10">
+        <f>IFERROR(过程品仓计算!L54+IF(过程品仓计算!O54="",0,过程品仓计算!O54)+IF(过程品仓计算!P54="",0,过程品仓计算!P54)+IF(过程品仓计算!Q54="",0,过程品仓计算!Q54),0)</f>
+        <v/>
+      </c>
+      <c r="S54" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R54/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6408,18 +7174,24 @@
         <v/>
       </c>
       <c r="L55" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H55,过程品仓计算!K55),0)</f>
-        <v/>
-      </c>
-      <c r="M55" s="9" t="n"/>
-      <c r="N55" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H55,过程品仓计算!K55)/MAX(1-IF(过程品仓计算!M55="",0,过程品仓计算!M55),0.01)*(1+IF(过程品仓计算!N55="",0,过程品仓计算!N55)),0)</f>
+        <v/>
+      </c>
+      <c r="M55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O55" s="9" t="n"/>
-      <c r="P55" s="10">
-        <f>IFERROR(过程品仓计算!L55+IF(过程品仓计算!M55="",0,过程品仓计算!M55)+IF(过程品仓计算!N55="",0,过程品仓计算!N55)+IF(过程品仓计算!O55="",0,过程品仓计算!O55),0)</f>
-        <v/>
-      </c>
-      <c r="Q55" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P55/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P55" s="9" t="n"/>
+      <c r="Q55" s="9" t="n"/>
+      <c r="R55" s="10">
+        <f>IFERROR(过程品仓计算!L55+IF(过程品仓计算!O55="",0,过程品仓计算!O55)+IF(过程品仓计算!P55="",0,过程品仓计算!P55)+IF(过程品仓计算!Q55="",0,过程品仓计算!Q55),0)</f>
+        <v/>
+      </c>
+      <c r="S55" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R55/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6465,18 +7237,24 @@
         <v/>
       </c>
       <c r="L56" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H56,过程品仓计算!K56),0)</f>
-        <v/>
-      </c>
-      <c r="M56" s="9" t="n"/>
-      <c r="N56" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H56,过程品仓计算!K56)/MAX(1-IF(过程品仓计算!M56="",0,过程品仓计算!M56),0.01)*(1+IF(过程品仓计算!N56="",0,过程品仓计算!N56)),0)</f>
+        <v/>
+      </c>
+      <c r="M56" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O56" s="9" t="n"/>
-      <c r="P56" s="10">
-        <f>IFERROR(过程品仓计算!L56+IF(过程品仓计算!M56="",0,过程品仓计算!M56)+IF(过程品仓计算!N56="",0,过程品仓计算!N56)+IF(过程品仓计算!O56="",0,过程品仓计算!O56),0)</f>
-        <v/>
-      </c>
-      <c r="Q56" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P56/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P56" s="9" t="n"/>
+      <c r="Q56" s="9" t="n"/>
+      <c r="R56" s="10">
+        <f>IFERROR(过程品仓计算!L56+IF(过程品仓计算!O56="",0,过程品仓计算!O56)+IF(过程品仓计算!P56="",0,过程品仓计算!P56)+IF(过程品仓计算!Q56="",0,过程品仓计算!Q56),0)</f>
+        <v/>
+      </c>
+      <c r="S56" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R56/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6522,18 +7300,24 @@
         <v/>
       </c>
       <c r="L57" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H57,过程品仓计算!K57),0)</f>
-        <v/>
-      </c>
-      <c r="M57" s="9" t="n"/>
-      <c r="N57" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H57,过程品仓计算!K57)/MAX(1-IF(过程品仓计算!M57="",0,过程品仓计算!M57),0.01)*(1+IF(过程品仓计算!N57="",0,过程品仓计算!N57)),0)</f>
+        <v/>
+      </c>
+      <c r="M57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O57" s="9" t="n"/>
-      <c r="P57" s="10">
-        <f>IFERROR(过程品仓计算!L57+IF(过程品仓计算!M57="",0,过程品仓计算!M57)+IF(过程品仓计算!N57="",0,过程品仓计算!N57)+IF(过程品仓计算!O57="",0,过程品仓计算!O57),0)</f>
-        <v/>
-      </c>
-      <c r="Q57" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P57/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P57" s="9" t="n"/>
+      <c r="Q57" s="9" t="n"/>
+      <c r="R57" s="10">
+        <f>IFERROR(过程品仓计算!L57+IF(过程品仓计算!O57="",0,过程品仓计算!O57)+IF(过程品仓计算!P57="",0,过程品仓计算!P57)+IF(过程品仓计算!Q57="",0,过程品仓计算!Q57),0)</f>
+        <v/>
+      </c>
+      <c r="S57" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R57/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6579,18 +7363,24 @@
         <v/>
       </c>
       <c r="L58" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H58,过程品仓计算!K58),0)</f>
-        <v/>
-      </c>
-      <c r="M58" s="9" t="n"/>
-      <c r="N58" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H58,过程品仓计算!K58)/MAX(1-IF(过程品仓计算!M58="",0,过程品仓计算!M58),0.01)*(1+IF(过程品仓计算!N58="",0,过程品仓计算!N58)),0)</f>
+        <v/>
+      </c>
+      <c r="M58" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O58" s="9" t="n"/>
-      <c r="P58" s="10">
-        <f>IFERROR(过程品仓计算!L58+IF(过程品仓计算!M58="",0,过程品仓计算!M58)+IF(过程品仓计算!N58="",0,过程品仓计算!N58)+IF(过程品仓计算!O58="",0,过程品仓计算!O58),0)</f>
-        <v/>
-      </c>
-      <c r="Q58" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P58/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P58" s="9" t="n"/>
+      <c r="Q58" s="9" t="n"/>
+      <c r="R58" s="10">
+        <f>IFERROR(过程品仓计算!L58+IF(过程品仓计算!O58="",0,过程品仓计算!O58)+IF(过程品仓计算!P58="",0,过程品仓计算!P58)+IF(过程品仓计算!Q58="",0,过程品仓计算!Q58),0)</f>
+        <v/>
+      </c>
+      <c r="S58" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R58/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6600,12 +7390,12 @@
           <t>低温碳化后暂存 小计</t>
         </is>
       </c>
-      <c r="P59" s="10">
-        <f>SUM(P47:P58)</f>
-        <v/>
-      </c>
-      <c r="Q59" s="10">
-        <f>SUM(Q47:Q58)</f>
+      <c r="R59" s="10">
+        <f>SUM(R47:R58)</f>
+        <v/>
+      </c>
+      <c r="S59" s="10">
+        <f>SUM(S47:S58)</f>
         <v/>
       </c>
     </row>
@@ -6658,18 +7448,26 @@
         <v/>
       </c>
       <c r="L61" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H61,过程品仓计算!K61),0)</f>
-        <v/>
-      </c>
-      <c r="M61" s="9" t="n"/>
-      <c r="N61" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H61,过程品仓计算!K61)/MAX(1-IF(过程品仓计算!M61="",0,过程品仓计算!M61),0.01)*(1+IF(过程品仓计算!N61="",0,过程品仓计算!N61)),0)</f>
+        <v/>
+      </c>
+      <c r="M61" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N61" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O61" s="9" t="n"/>
-      <c r="P61" s="10">
-        <f>IFERROR(过程品仓计算!L61+IF(过程品仓计算!M61="",0,过程品仓计算!M61)+IF(过程品仓计算!N61="",0,过程品仓计算!N61)+IF(过程品仓计算!O61="",0,过程品仓计算!O61),0)</f>
-        <v/>
-      </c>
-      <c r="Q61" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P61/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P61" s="9" t="n"/>
+      <c r="Q61" s="9" t="n"/>
+      <c r="R61" s="10">
+        <f>IFERROR(过程品仓计算!L61+IF(过程品仓计算!O61="",0,过程品仓计算!O61)+IF(过程品仓计算!P61="",0,过程品仓计算!P61)+IF(过程品仓计算!Q61="",0,过程品仓计算!Q61),0)</f>
+        <v/>
+      </c>
+      <c r="S61" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R61/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6715,18 +7513,26 @@
         <v/>
       </c>
       <c r="L62" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H62,过程品仓计算!K62),0)</f>
-        <v/>
-      </c>
-      <c r="M62" s="9" t="n"/>
-      <c r="N62" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H62,过程品仓计算!K62)/MAX(1-IF(过程品仓计算!M62="",0,过程品仓计算!M62),0.01)*(1+IF(过程品仓计算!N62="",0,过程品仓计算!N62)),0)</f>
+        <v/>
+      </c>
+      <c r="M62" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N62" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O62" s="9" t="n"/>
-      <c r="P62" s="10">
-        <f>IFERROR(过程品仓计算!L62+IF(过程品仓计算!M62="",0,过程品仓计算!M62)+IF(过程品仓计算!N62="",0,过程品仓计算!N62)+IF(过程品仓计算!O62="",0,过程品仓计算!O62),0)</f>
-        <v/>
-      </c>
-      <c r="Q62" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P62/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P62" s="9" t="n"/>
+      <c r="Q62" s="9" t="n"/>
+      <c r="R62" s="10">
+        <f>IFERROR(过程品仓计算!L62+IF(过程品仓计算!O62="",0,过程品仓计算!O62)+IF(过程品仓计算!P62="",0,过程品仓计算!P62)+IF(过程品仓计算!Q62="",0,过程品仓计算!Q62),0)</f>
+        <v/>
+      </c>
+      <c r="S62" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R62/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6772,18 +7578,26 @@
         <v/>
       </c>
       <c r="L63" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H63,过程品仓计算!K63),0)</f>
-        <v/>
-      </c>
-      <c r="M63" s="9" t="n"/>
-      <c r="N63" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H63,过程品仓计算!K63)/MAX(1-IF(过程品仓计算!M63="",0,过程品仓计算!M63),0.01)*(1+IF(过程品仓计算!N63="",0,过程品仓计算!N63)),0)</f>
+        <v/>
+      </c>
+      <c r="M63" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N63" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O63" s="9" t="n"/>
-      <c r="P63" s="10">
-        <f>IFERROR(过程品仓计算!L63+IF(过程品仓计算!M63="",0,过程品仓计算!M63)+IF(过程品仓计算!N63="",0,过程品仓计算!N63)+IF(过程品仓计算!O63="",0,过程品仓计算!O63),0)</f>
-        <v/>
-      </c>
-      <c r="Q63" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P63/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P63" s="9" t="n"/>
+      <c r="Q63" s="9" t="n"/>
+      <c r="R63" s="10">
+        <f>IFERROR(过程品仓计算!L63+IF(过程品仓计算!O63="",0,过程品仓计算!O63)+IF(过程品仓计算!P63="",0,过程品仓计算!P63)+IF(过程品仓计算!Q63="",0,过程品仓计算!Q63),0)</f>
+        <v/>
+      </c>
+      <c r="S63" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R63/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6829,18 +7643,26 @@
         <v/>
       </c>
       <c r="L64" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H64,过程品仓计算!K64),0)</f>
-        <v/>
-      </c>
-      <c r="M64" s="9" t="n"/>
-      <c r="N64" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H64,过程品仓计算!K64)/MAX(1-IF(过程品仓计算!M64="",0,过程品仓计算!M64),0.01)*(1+IF(过程品仓计算!N64="",0,过程品仓计算!N64)),0)</f>
+        <v/>
+      </c>
+      <c r="M64" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N64" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O64" s="9" t="n"/>
-      <c r="P64" s="10">
-        <f>IFERROR(过程品仓计算!L64+IF(过程品仓计算!M64="",0,过程品仓计算!M64)+IF(过程品仓计算!N64="",0,过程品仓计算!N64)+IF(过程品仓计算!O64="",0,过程品仓计算!O64),0)</f>
-        <v/>
-      </c>
-      <c r="Q64" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P64/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P64" s="9" t="n"/>
+      <c r="Q64" s="9" t="n"/>
+      <c r="R64" s="10">
+        <f>IFERROR(过程品仓计算!L64+IF(过程品仓计算!O64="",0,过程品仓计算!O64)+IF(过程品仓计算!P64="",0,过程品仓计算!P64)+IF(过程品仓计算!Q64="",0,过程品仓计算!Q64),0)</f>
+        <v/>
+      </c>
+      <c r="S64" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R64/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6886,18 +7708,26 @@
         <v/>
       </c>
       <c r="L65" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H65,过程品仓计算!K65),0)</f>
-        <v/>
-      </c>
-      <c r="M65" s="9" t="n"/>
-      <c r="N65" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H65,过程品仓计算!K65)/MAX(1-IF(过程品仓计算!M65="",0,过程品仓计算!M65),0.01)*(1+IF(过程品仓计算!N65="",0,过程品仓计算!N65)),0)</f>
+        <v/>
+      </c>
+      <c r="M65" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N65" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O65" s="9" t="n"/>
-      <c r="P65" s="10">
-        <f>IFERROR(过程品仓计算!L65+IF(过程品仓计算!M65="",0,过程品仓计算!M65)+IF(过程品仓计算!N65="",0,过程品仓计算!N65)+IF(过程品仓计算!O65="",0,过程品仓计算!O65),0)</f>
-        <v/>
-      </c>
-      <c r="Q65" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P65/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P65" s="9" t="n"/>
+      <c r="Q65" s="9" t="n"/>
+      <c r="R65" s="10">
+        <f>IFERROR(过程品仓计算!L65+IF(过程品仓计算!O65="",0,过程品仓计算!O65)+IF(过程品仓计算!P65="",0,过程品仓计算!P65)+IF(过程品仓计算!Q65="",0,过程品仓计算!Q65),0)</f>
+        <v/>
+      </c>
+      <c r="S65" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R65/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -6943,18 +7773,26 @@
         <v/>
       </c>
       <c r="L66" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H66,过程品仓计算!K66),0)</f>
-        <v/>
-      </c>
-      <c r="M66" s="9" t="n"/>
-      <c r="N66" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H66,过程品仓计算!K66)/MAX(1-IF(过程品仓计算!M66="",0,过程品仓计算!M66),0.01)*(1+IF(过程品仓计算!N66="",0,过程品仓计算!N66)),0)</f>
+        <v/>
+      </c>
+      <c r="M66" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N66" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O66" s="9" t="n"/>
-      <c r="P66" s="10">
-        <f>IFERROR(过程品仓计算!L66+IF(过程品仓计算!M66="",0,过程品仓计算!M66)+IF(过程品仓计算!N66="",0,过程品仓计算!N66)+IF(过程品仓计算!O66="",0,过程品仓计算!O66),0)</f>
-        <v/>
-      </c>
-      <c r="Q66" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P66/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P66" s="9" t="n"/>
+      <c r="Q66" s="9" t="n"/>
+      <c r="R66" s="10">
+        <f>IFERROR(过程品仓计算!L66+IF(过程品仓计算!O66="",0,过程品仓计算!O66)+IF(过程品仓计算!P66="",0,过程品仓计算!P66)+IF(过程品仓计算!Q66="",0,过程品仓计算!Q66),0)</f>
+        <v/>
+      </c>
+      <c r="S66" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R66/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7000,18 +7838,26 @@
         <v/>
       </c>
       <c r="L67" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H67,过程品仓计算!K67),0)</f>
-        <v/>
-      </c>
-      <c r="M67" s="9" t="n"/>
-      <c r="N67" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H67,过程品仓计算!K67)/MAX(1-IF(过程品仓计算!M67="",0,过程品仓计算!M67),0.01)*(1+IF(过程品仓计算!N67="",0,过程品仓计算!N67)),0)</f>
+        <v/>
+      </c>
+      <c r="M67" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N67" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O67" s="9" t="n"/>
-      <c r="P67" s="10">
-        <f>IFERROR(过程品仓计算!L67+IF(过程品仓计算!M67="",0,过程品仓计算!M67)+IF(过程品仓计算!N67="",0,过程品仓计算!N67)+IF(过程品仓计算!O67="",0,过程品仓计算!O67),0)</f>
-        <v/>
-      </c>
-      <c r="Q67" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P67/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P67" s="9" t="n"/>
+      <c r="Q67" s="9" t="n"/>
+      <c r="R67" s="10">
+        <f>IFERROR(过程品仓计算!L67+IF(过程品仓计算!O67="",0,过程品仓计算!O67)+IF(过程品仓计算!P67="",0,过程品仓计算!P67)+IF(过程品仓计算!Q67="",0,过程品仓计算!Q67),0)</f>
+        <v/>
+      </c>
+      <c r="S67" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R67/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7057,18 +7903,26 @@
         <v/>
       </c>
       <c r="L68" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H68,过程品仓计算!K68),0)</f>
-        <v/>
-      </c>
-      <c r="M68" s="9" t="n"/>
-      <c r="N68" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H68,过程品仓计算!K68)/MAX(1-IF(过程品仓计算!M68="",0,过程品仓计算!M68),0.01)*(1+IF(过程品仓计算!N68="",0,过程品仓计算!N68)),0)</f>
+        <v/>
+      </c>
+      <c r="M68" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N68" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O68" s="9" t="n"/>
-      <c r="P68" s="10">
-        <f>IFERROR(过程品仓计算!L68+IF(过程品仓计算!M68="",0,过程品仓计算!M68)+IF(过程品仓计算!N68="",0,过程品仓计算!N68)+IF(过程品仓计算!O68="",0,过程品仓计算!O68),0)</f>
-        <v/>
-      </c>
-      <c r="Q68" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P68/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P68" s="9" t="n"/>
+      <c r="Q68" s="9" t="n"/>
+      <c r="R68" s="10">
+        <f>IFERROR(过程品仓计算!L68+IF(过程品仓计算!O68="",0,过程品仓计算!O68)+IF(过程品仓计算!P68="",0,过程品仓计算!P68)+IF(过程品仓计算!Q68="",0,过程品仓计算!Q68),0)</f>
+        <v/>
+      </c>
+      <c r="S68" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R68/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7114,18 +7968,26 @@
         <v/>
       </c>
       <c r="L69" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H69,过程品仓计算!K69),0)</f>
-        <v/>
-      </c>
-      <c r="M69" s="9" t="n"/>
-      <c r="N69" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H69,过程品仓计算!K69)/MAX(1-IF(过程品仓计算!M69="",0,过程品仓计算!M69),0.01)*(1+IF(过程品仓计算!N69="",0,过程品仓计算!N69)),0)</f>
+        <v/>
+      </c>
+      <c r="M69" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N69" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O69" s="9" t="n"/>
-      <c r="P69" s="10">
-        <f>IFERROR(过程品仓计算!L69+IF(过程品仓计算!M69="",0,过程品仓计算!M69)+IF(过程品仓计算!N69="",0,过程品仓计算!N69)+IF(过程品仓计算!O69="",0,过程品仓计算!O69),0)</f>
-        <v/>
-      </c>
-      <c r="Q69" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P69/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P69" s="9" t="n"/>
+      <c r="Q69" s="9" t="n"/>
+      <c r="R69" s="10">
+        <f>IFERROR(过程品仓计算!L69+IF(过程品仓计算!O69="",0,过程品仓计算!O69)+IF(过程品仓计算!P69="",0,过程品仓计算!P69)+IF(过程品仓计算!Q69="",0,过程品仓计算!Q69),0)</f>
+        <v/>
+      </c>
+      <c r="S69" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R69/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7171,18 +8033,26 @@
         <v/>
       </c>
       <c r="L70" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H70,过程品仓计算!K70),0)</f>
-        <v/>
-      </c>
-      <c r="M70" s="9" t="n"/>
-      <c r="N70" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H70,过程品仓计算!K70)/MAX(1-IF(过程品仓计算!M70="",0,过程品仓计算!M70),0.01)*(1+IF(过程品仓计算!N70="",0,过程品仓计算!N70)),0)</f>
+        <v/>
+      </c>
+      <c r="M70" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N70" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O70" s="9" t="n"/>
-      <c r="P70" s="10">
-        <f>IFERROR(过程品仓计算!L70+IF(过程品仓计算!M70="",0,过程品仓计算!M70)+IF(过程品仓计算!N70="",0,过程品仓计算!N70)+IF(过程品仓计算!O70="",0,过程品仓计算!O70),0)</f>
-        <v/>
-      </c>
-      <c r="Q70" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P70/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P70" s="9" t="n"/>
+      <c r="Q70" s="9" t="n"/>
+      <c r="R70" s="10">
+        <f>IFERROR(过程品仓计算!L70+IF(过程品仓计算!O70="",0,过程品仓计算!O70)+IF(过程品仓计算!P70="",0,过程品仓计算!P70)+IF(过程品仓计算!Q70="",0,过程品仓计算!Q70),0)</f>
+        <v/>
+      </c>
+      <c r="S70" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R70/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7228,18 +8098,26 @@
         <v/>
       </c>
       <c r="L71" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H71,过程品仓计算!K71),0)</f>
-        <v/>
-      </c>
-      <c r="M71" s="9" t="n"/>
-      <c r="N71" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H71,过程品仓计算!K71)/MAX(1-IF(过程品仓计算!M71="",0,过程品仓计算!M71),0.01)*(1+IF(过程品仓计算!N71="",0,过程品仓计算!N71)),0)</f>
+        <v/>
+      </c>
+      <c r="M71" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N71" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O71" s="9" t="n"/>
-      <c r="P71" s="10">
-        <f>IFERROR(过程品仓计算!L71+IF(过程品仓计算!M71="",0,过程品仓计算!M71)+IF(过程品仓计算!N71="",0,过程品仓计算!N71)+IF(过程品仓计算!O71="",0,过程品仓计算!O71),0)</f>
-        <v/>
-      </c>
-      <c r="Q71" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P71/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P71" s="9" t="n"/>
+      <c r="Q71" s="9" t="n"/>
+      <c r="R71" s="10">
+        <f>IFERROR(过程品仓计算!L71+IF(过程品仓计算!O71="",0,过程品仓计算!O71)+IF(过程品仓计算!P71="",0,过程品仓计算!P71)+IF(过程品仓计算!Q71="",0,过程品仓计算!Q71),0)</f>
+        <v/>
+      </c>
+      <c r="S71" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R71/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7285,18 +8163,26 @@
         <v/>
       </c>
       <c r="L72" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H72,过程品仓计算!K72),0)</f>
-        <v/>
-      </c>
-      <c r="M72" s="9" t="n"/>
-      <c r="N72" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H72,过程品仓计算!K72)/MAX(1-IF(过程品仓计算!M72="",0,过程品仓计算!M72),0.01)*(1+IF(过程品仓计算!N72="",0,过程品仓计算!N72)),0)</f>
+        <v/>
+      </c>
+      <c r="M72" s="10">
+        <f>参数设置!$C$28</f>
+        <v/>
+      </c>
+      <c r="N72" s="10">
+        <f>参数设置!$C$29</f>
+        <v/>
+      </c>
       <c r="O72" s="9" t="n"/>
-      <c r="P72" s="10">
-        <f>IFERROR(过程品仓计算!L72+IF(过程品仓计算!M72="",0,过程品仓计算!M72)+IF(过程品仓计算!N72="",0,过程品仓计算!N72)+IF(过程品仓计算!O72="",0,过程品仓计算!O72),0)</f>
-        <v/>
-      </c>
-      <c r="Q72" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P72/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P72" s="9" t="n"/>
+      <c r="Q72" s="9" t="n"/>
+      <c r="R72" s="10">
+        <f>IFERROR(过程品仓计算!L72+IF(过程品仓计算!O72="",0,过程品仓计算!O72)+IF(过程品仓计算!P72="",0,过程品仓计算!P72)+IF(过程品仓计算!Q72="",0,过程品仓计算!Q72),0)</f>
+        <v/>
+      </c>
+      <c r="S72" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R72/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7306,12 +8192,12 @@
           <t>石墨化后暂存 小计</t>
         </is>
       </c>
-      <c r="P73" s="10">
-        <f>SUM(P61:P72)</f>
-        <v/>
-      </c>
-      <c r="Q73" s="10">
-        <f>SUM(Q61:Q72)</f>
+      <c r="R73" s="10">
+        <f>SUM(R61:R72)</f>
+        <v/>
+      </c>
+      <c r="S73" s="10">
+        <f>SUM(S61:S72)</f>
         <v/>
       </c>
     </row>
@@ -7364,18 +8250,24 @@
         <v/>
       </c>
       <c r="L75" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H75,过程品仓计算!K75),0)</f>
-        <v/>
-      </c>
-      <c r="M75" s="9" t="n"/>
-      <c r="N75" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H75,过程品仓计算!K75)/MAX(1-IF(过程品仓计算!M75="",0,过程品仓计算!M75),0.01)*(1+IF(过程品仓计算!N75="",0,过程品仓计算!N75)),0)</f>
+        <v/>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O75" s="9" t="n"/>
-      <c r="P75" s="10">
-        <f>IFERROR(过程品仓计算!L75+IF(过程品仓计算!M75="",0,过程品仓计算!M75)+IF(过程品仓计算!N75="",0,过程品仓计算!N75)+IF(过程品仓计算!O75="",0,过程品仓计算!O75),0)</f>
-        <v/>
-      </c>
-      <c r="Q75" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P75/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P75" s="9" t="n"/>
+      <c r="Q75" s="9" t="n"/>
+      <c r="R75" s="10">
+        <f>IFERROR(过程品仓计算!L75+IF(过程品仓计算!O75="",0,过程品仓计算!O75)+IF(过程品仓计算!P75="",0,过程品仓计算!P75)+IF(过程品仓计算!Q75="",0,过程品仓计算!Q75),0)</f>
+        <v/>
+      </c>
+      <c r="S75" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R75/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7421,18 +8313,24 @@
         <v/>
       </c>
       <c r="L76" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H76,过程品仓计算!K76),0)</f>
-        <v/>
-      </c>
-      <c r="M76" s="9" t="n"/>
-      <c r="N76" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H76,过程品仓计算!K76)/MAX(1-IF(过程品仓计算!M76="",0,过程品仓计算!M76),0.01)*(1+IF(过程品仓计算!N76="",0,过程品仓计算!N76)),0)</f>
+        <v/>
+      </c>
+      <c r="M76" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O76" s="9" t="n"/>
-      <c r="P76" s="10">
-        <f>IFERROR(过程品仓计算!L76+IF(过程品仓计算!M76="",0,过程品仓计算!M76)+IF(过程品仓计算!N76="",0,过程品仓计算!N76)+IF(过程品仓计算!O76="",0,过程品仓计算!O76),0)</f>
-        <v/>
-      </c>
-      <c r="Q76" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P76/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P76" s="9" t="n"/>
+      <c r="Q76" s="9" t="n"/>
+      <c r="R76" s="10">
+        <f>IFERROR(过程品仓计算!L76+IF(过程品仓计算!O76="",0,过程品仓计算!O76)+IF(过程品仓计算!P76="",0,过程品仓计算!P76)+IF(过程品仓计算!Q76="",0,过程品仓计算!Q76),0)</f>
+        <v/>
+      </c>
+      <c r="S76" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R76/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7478,18 +8376,24 @@
         <v/>
       </c>
       <c r="L77" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H77,过程品仓计算!K77),0)</f>
-        <v/>
-      </c>
-      <c r="M77" s="9" t="n"/>
-      <c r="N77" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H77,过程品仓计算!K77)/MAX(1-IF(过程品仓计算!M77="",0,过程品仓计算!M77),0.01)*(1+IF(过程品仓计算!N77="",0,过程品仓计算!N77)),0)</f>
+        <v/>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O77" s="9" t="n"/>
-      <c r="P77" s="10">
-        <f>IFERROR(过程品仓计算!L77+IF(过程品仓计算!M77="",0,过程品仓计算!M77)+IF(过程品仓计算!N77="",0,过程品仓计算!N77)+IF(过程品仓计算!O77="",0,过程品仓计算!O77),0)</f>
-        <v/>
-      </c>
-      <c r="Q77" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P77/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P77" s="9" t="n"/>
+      <c r="Q77" s="9" t="n"/>
+      <c r="R77" s="10">
+        <f>IFERROR(过程品仓计算!L77+IF(过程品仓计算!O77="",0,过程品仓计算!O77)+IF(过程品仓计算!P77="",0,过程品仓计算!P77)+IF(过程品仓计算!Q77="",0,过程品仓计算!Q77),0)</f>
+        <v/>
+      </c>
+      <c r="S77" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R77/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7535,18 +8439,24 @@
         <v/>
       </c>
       <c r="L78" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H78,过程品仓计算!K78),0)</f>
-        <v/>
-      </c>
-      <c r="M78" s="9" t="n"/>
-      <c r="N78" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H78,过程品仓计算!K78)/MAX(1-IF(过程品仓计算!M78="",0,过程品仓计算!M78),0.01)*(1+IF(过程品仓计算!N78="",0,过程品仓计算!N78)),0)</f>
+        <v/>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O78" s="9" t="n"/>
-      <c r="P78" s="10">
-        <f>IFERROR(过程品仓计算!L78+IF(过程品仓计算!M78="",0,过程品仓计算!M78)+IF(过程品仓计算!N78="",0,过程品仓计算!N78)+IF(过程品仓计算!O78="",0,过程品仓计算!O78),0)</f>
-        <v/>
-      </c>
-      <c r="Q78" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P78/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P78" s="9" t="n"/>
+      <c r="Q78" s="9" t="n"/>
+      <c r="R78" s="10">
+        <f>IFERROR(过程品仓计算!L78+IF(过程品仓计算!O78="",0,过程品仓计算!O78)+IF(过程品仓计算!P78="",0,过程品仓计算!P78)+IF(过程品仓计算!Q78="",0,过程品仓计算!Q78),0)</f>
+        <v/>
+      </c>
+      <c r="S78" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R78/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7592,18 +8502,24 @@
         <v/>
       </c>
       <c r="L79" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H79,过程品仓计算!K79),0)</f>
-        <v/>
-      </c>
-      <c r="M79" s="9" t="n"/>
-      <c r="N79" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H79,过程品仓计算!K79)/MAX(1-IF(过程品仓计算!M79="",0,过程品仓计算!M79),0.01)*(1+IF(过程品仓计算!N79="",0,过程品仓计算!N79)),0)</f>
+        <v/>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O79" s="9" t="n"/>
-      <c r="P79" s="10">
-        <f>IFERROR(过程品仓计算!L79+IF(过程品仓计算!M79="",0,过程品仓计算!M79)+IF(过程品仓计算!N79="",0,过程品仓计算!N79)+IF(过程品仓计算!O79="",0,过程品仓计算!O79),0)</f>
-        <v/>
-      </c>
-      <c r="Q79" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P79/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P79" s="9" t="n"/>
+      <c r="Q79" s="9" t="n"/>
+      <c r="R79" s="10">
+        <f>IFERROR(过程品仓计算!L79+IF(过程品仓计算!O79="",0,过程品仓计算!O79)+IF(过程品仓计算!P79="",0,过程品仓计算!P79)+IF(过程品仓计算!Q79="",0,过程品仓计算!Q79),0)</f>
+        <v/>
+      </c>
+      <c r="S79" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R79/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7649,18 +8565,24 @@
         <v/>
       </c>
       <c r="L80" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H80,过程品仓计算!K80),0)</f>
-        <v/>
-      </c>
-      <c r="M80" s="9" t="n"/>
-      <c r="N80" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H80,过程品仓计算!K80)/MAX(1-IF(过程品仓计算!M80="",0,过程品仓计算!M80),0.01)*(1+IF(过程品仓计算!N80="",0,过程品仓计算!N80)),0)</f>
+        <v/>
+      </c>
+      <c r="M80" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O80" s="9" t="n"/>
-      <c r="P80" s="10">
-        <f>IFERROR(过程品仓计算!L80+IF(过程品仓计算!M80="",0,过程品仓计算!M80)+IF(过程品仓计算!N80="",0,过程品仓计算!N80)+IF(过程品仓计算!O80="",0,过程品仓计算!O80),0)</f>
-        <v/>
-      </c>
-      <c r="Q80" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P80/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P80" s="9" t="n"/>
+      <c r="Q80" s="9" t="n"/>
+      <c r="R80" s="10">
+        <f>IFERROR(过程品仓计算!L80+IF(过程品仓计算!O80="",0,过程品仓计算!O80)+IF(过程品仓计算!P80="",0,过程品仓计算!P80)+IF(过程品仓计算!Q80="",0,过程品仓计算!Q80),0)</f>
+        <v/>
+      </c>
+      <c r="S80" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R80/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7706,18 +8628,24 @@
         <v/>
       </c>
       <c r="L81" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H81,过程品仓计算!K81),0)</f>
-        <v/>
-      </c>
-      <c r="M81" s="9" t="n"/>
-      <c r="N81" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H81,过程品仓计算!K81)/MAX(1-IF(过程品仓计算!M81="",0,过程品仓计算!M81),0.01)*(1+IF(过程品仓计算!N81="",0,过程品仓计算!N81)),0)</f>
+        <v/>
+      </c>
+      <c r="M81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O81" s="9" t="n"/>
-      <c r="P81" s="10">
-        <f>IFERROR(过程品仓计算!L81+IF(过程品仓计算!M81="",0,过程品仓计算!M81)+IF(过程品仓计算!N81="",0,过程品仓计算!N81)+IF(过程品仓计算!O81="",0,过程品仓计算!O81),0)</f>
-        <v/>
-      </c>
-      <c r="Q81" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P81/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P81" s="9" t="n"/>
+      <c r="Q81" s="9" t="n"/>
+      <c r="R81" s="10">
+        <f>IFERROR(过程品仓计算!L81+IF(过程品仓计算!O81="",0,过程品仓计算!O81)+IF(过程品仓计算!P81="",0,过程品仓计算!P81)+IF(过程品仓计算!Q81="",0,过程品仓计算!Q81),0)</f>
+        <v/>
+      </c>
+      <c r="S81" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R81/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7763,18 +8691,24 @@
         <v/>
       </c>
       <c r="L82" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H82,过程品仓计算!K82),0)</f>
-        <v/>
-      </c>
-      <c r="M82" s="9" t="n"/>
-      <c r="N82" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H82,过程品仓计算!K82)/MAX(1-IF(过程品仓计算!M82="",0,过程品仓计算!M82),0.01)*(1+IF(过程品仓计算!N82="",0,过程品仓计算!N82)),0)</f>
+        <v/>
+      </c>
+      <c r="M82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O82" s="9" t="n"/>
-      <c r="P82" s="10">
-        <f>IFERROR(过程品仓计算!L82+IF(过程品仓计算!M82="",0,过程品仓计算!M82)+IF(过程品仓计算!N82="",0,过程品仓计算!N82)+IF(过程品仓计算!O82="",0,过程品仓计算!O82),0)</f>
-        <v/>
-      </c>
-      <c r="Q82" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P82/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P82" s="9" t="n"/>
+      <c r="Q82" s="9" t="n"/>
+      <c r="R82" s="10">
+        <f>IFERROR(过程品仓计算!L82+IF(过程品仓计算!O82="",0,过程品仓计算!O82)+IF(过程品仓计算!P82="",0,过程品仓计算!P82)+IF(过程品仓计算!Q82="",0,过程品仓计算!Q82),0)</f>
+        <v/>
+      </c>
+      <c r="S82" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R82/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7820,18 +8754,24 @@
         <v/>
       </c>
       <c r="L83" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H83,过程品仓计算!K83),0)</f>
-        <v/>
-      </c>
-      <c r="M83" s="9" t="n"/>
-      <c r="N83" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H83,过程品仓计算!K83)/MAX(1-IF(过程品仓计算!M83="",0,过程品仓计算!M83),0.01)*(1+IF(过程品仓计算!N83="",0,过程品仓计算!N83)),0)</f>
+        <v/>
+      </c>
+      <c r="M83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O83" s="9" t="n"/>
-      <c r="P83" s="10">
-        <f>IFERROR(过程品仓计算!L83+IF(过程品仓计算!M83="",0,过程品仓计算!M83)+IF(过程品仓计算!N83="",0,过程品仓计算!N83)+IF(过程品仓计算!O83="",0,过程品仓计算!O83),0)</f>
-        <v/>
-      </c>
-      <c r="Q83" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P83/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P83" s="9" t="n"/>
+      <c r="Q83" s="9" t="n"/>
+      <c r="R83" s="10">
+        <f>IFERROR(过程品仓计算!L83+IF(过程品仓计算!O83="",0,过程品仓计算!O83)+IF(过程品仓计算!P83="",0,过程品仓计算!P83)+IF(过程品仓计算!Q83="",0,过程品仓计算!Q83),0)</f>
+        <v/>
+      </c>
+      <c r="S83" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R83/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7877,18 +8817,24 @@
         <v/>
       </c>
       <c r="L84" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H84,过程品仓计算!K84),0)</f>
-        <v/>
-      </c>
-      <c r="M84" s="9" t="n"/>
-      <c r="N84" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H84,过程品仓计算!K84)/MAX(1-IF(过程品仓计算!M84="",0,过程品仓计算!M84),0.01)*(1+IF(过程品仓计算!N84="",0,过程品仓计算!N84)),0)</f>
+        <v/>
+      </c>
+      <c r="M84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O84" s="9" t="n"/>
-      <c r="P84" s="10">
-        <f>IFERROR(过程品仓计算!L84+IF(过程品仓计算!M84="",0,过程品仓计算!M84)+IF(过程品仓计算!N84="",0,过程品仓计算!N84)+IF(过程品仓计算!O84="",0,过程品仓计算!O84),0)</f>
-        <v/>
-      </c>
-      <c r="Q84" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P84/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P84" s="9" t="n"/>
+      <c r="Q84" s="9" t="n"/>
+      <c r="R84" s="10">
+        <f>IFERROR(过程品仓计算!L84+IF(过程品仓计算!O84="",0,过程品仓计算!O84)+IF(过程品仓计算!P84="",0,过程品仓计算!P84)+IF(过程品仓计算!Q84="",0,过程品仓计算!Q84),0)</f>
+        <v/>
+      </c>
+      <c r="S84" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R84/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7934,18 +8880,24 @@
         <v/>
       </c>
       <c r="L85" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H85,过程品仓计算!K85),0)</f>
-        <v/>
-      </c>
-      <c r="M85" s="9" t="n"/>
-      <c r="N85" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H85,过程品仓计算!K85)/MAX(1-IF(过程品仓计算!M85="",0,过程品仓计算!M85),0.01)*(1+IF(过程品仓计算!N85="",0,过程品仓计算!N85)),0)</f>
+        <v/>
+      </c>
+      <c r="M85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O85" s="9" t="n"/>
-      <c r="P85" s="10">
-        <f>IFERROR(过程品仓计算!L85+IF(过程品仓计算!M85="",0,过程品仓计算!M85)+IF(过程品仓计算!N85="",0,过程品仓计算!N85)+IF(过程品仓计算!O85="",0,过程品仓计算!O85),0)</f>
-        <v/>
-      </c>
-      <c r="Q85" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P85/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P85" s="9" t="n"/>
+      <c r="Q85" s="9" t="n"/>
+      <c r="R85" s="10">
+        <f>IFERROR(过程品仓计算!L85+IF(过程品仓计算!O85="",0,过程品仓计算!O85)+IF(过程品仓计算!P85="",0,过程品仓计算!P85)+IF(过程品仓计算!Q85="",0,过程品仓计算!Q85),0)</f>
+        <v/>
+      </c>
+      <c r="S85" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R85/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -7991,18 +8943,24 @@
         <v/>
       </c>
       <c r="L86" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H86,过程品仓计算!K86),0)</f>
-        <v/>
-      </c>
-      <c r="M86" s="9" t="n"/>
-      <c r="N86" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H86,过程品仓计算!K86)/MAX(1-IF(过程品仓计算!M86="",0,过程品仓计算!M86),0.01)*(1+IF(过程品仓计算!N86="",0,过程品仓计算!N86)),0)</f>
+        <v/>
+      </c>
+      <c r="M86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O86" s="9" t="n"/>
-      <c r="P86" s="10">
-        <f>IFERROR(过程品仓计算!L86+IF(过程品仓计算!M86="",0,过程品仓计算!M86)+IF(过程品仓计算!N86="",0,过程品仓计算!N86)+IF(过程品仓计算!O86="",0,过程品仓计算!O86),0)</f>
-        <v/>
-      </c>
-      <c r="Q86" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P86/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P86" s="9" t="n"/>
+      <c r="Q86" s="9" t="n"/>
+      <c r="R86" s="10">
+        <f>IFERROR(过程品仓计算!L86+IF(过程品仓计算!O86="",0,过程品仓计算!O86)+IF(过程品仓计算!P86="",0,过程品仓计算!P86)+IF(过程品仓计算!Q86="",0,过程品仓计算!Q86),0)</f>
+        <v/>
+      </c>
+      <c r="S86" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R86/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8012,12 +8970,12 @@
           <t>高温碳化后暂存 小计</t>
         </is>
       </c>
-      <c r="P87" s="10">
-        <f>SUM(P75:P86)</f>
-        <v/>
-      </c>
-      <c r="Q87" s="10">
-        <f>SUM(Q75:Q86)</f>
+      <c r="R87" s="10">
+        <f>SUM(R75:R86)</f>
+        <v/>
+      </c>
+      <c r="S87" s="10">
+        <f>SUM(S75:S86)</f>
         <v/>
       </c>
     </row>
@@ -8070,18 +9028,24 @@
         <v/>
       </c>
       <c r="L89" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H89,过程品仓计算!K89),0)</f>
-        <v/>
-      </c>
-      <c r="M89" s="9" t="n"/>
-      <c r="N89" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H89,过程品仓计算!K89)/MAX(1-IF(过程品仓计算!M89="",0,过程品仓计算!M89),0.01)*(1+IF(过程品仓计算!N89="",0,过程品仓计算!N89)),0)</f>
+        <v/>
+      </c>
+      <c r="M89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O89" s="9" t="n"/>
-      <c r="P89" s="10">
-        <f>IFERROR(过程品仓计算!L89+IF(过程品仓计算!M89="",0,过程品仓计算!M89)+IF(过程品仓计算!N89="",0,过程品仓计算!N89)+IF(过程品仓计算!O89="",0,过程品仓计算!O89),0)</f>
-        <v/>
-      </c>
-      <c r="Q89" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P89/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P89" s="9" t="n"/>
+      <c r="Q89" s="9" t="n"/>
+      <c r="R89" s="10">
+        <f>IFERROR(过程品仓计算!L89+IF(过程品仓计算!O89="",0,过程品仓计算!O89)+IF(过程品仓计算!P89="",0,过程品仓计算!P89)+IF(过程品仓计算!Q89="",0,过程品仓计算!Q89),0)</f>
+        <v/>
+      </c>
+      <c r="S89" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R89/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8127,18 +9091,24 @@
         <v/>
       </c>
       <c r="L90" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H90,过程品仓计算!K90),0)</f>
-        <v/>
-      </c>
-      <c r="M90" s="9" t="n"/>
-      <c r="N90" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H90,过程品仓计算!K90)/MAX(1-IF(过程品仓计算!M90="",0,过程品仓计算!M90),0.01)*(1+IF(过程品仓计算!N90="",0,过程品仓计算!N90)),0)</f>
+        <v/>
+      </c>
+      <c r="M90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O90" s="9" t="n"/>
-      <c r="P90" s="10">
-        <f>IFERROR(过程品仓计算!L90+IF(过程品仓计算!M90="",0,过程品仓计算!M90)+IF(过程品仓计算!N90="",0,过程品仓计算!N90)+IF(过程品仓计算!O90="",0,过程品仓计算!O90),0)</f>
-        <v/>
-      </c>
-      <c r="Q90" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P90/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P90" s="9" t="n"/>
+      <c r="Q90" s="9" t="n"/>
+      <c r="R90" s="10">
+        <f>IFERROR(过程品仓计算!L90+IF(过程品仓计算!O90="",0,过程品仓计算!O90)+IF(过程品仓计算!P90="",0,过程品仓计算!P90)+IF(过程品仓计算!Q90="",0,过程品仓计算!Q90),0)</f>
+        <v/>
+      </c>
+      <c r="S90" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R90/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8184,18 +9154,24 @@
         <v/>
       </c>
       <c r="L91" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H91,过程品仓计算!K91),0)</f>
-        <v/>
-      </c>
-      <c r="M91" s="9" t="n"/>
-      <c r="N91" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H91,过程品仓计算!K91)/MAX(1-IF(过程品仓计算!M91="",0,过程品仓计算!M91),0.01)*(1+IF(过程品仓计算!N91="",0,过程品仓计算!N91)),0)</f>
+        <v/>
+      </c>
+      <c r="M91" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O91" s="9" t="n"/>
-      <c r="P91" s="10">
-        <f>IFERROR(过程品仓计算!L91+IF(过程品仓计算!M91="",0,过程品仓计算!M91)+IF(过程品仓计算!N91="",0,过程品仓计算!N91)+IF(过程品仓计算!O91="",0,过程品仓计算!O91),0)</f>
-        <v/>
-      </c>
-      <c r="Q91" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P91/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P91" s="9" t="n"/>
+      <c r="Q91" s="9" t="n"/>
+      <c r="R91" s="10">
+        <f>IFERROR(过程品仓计算!L91+IF(过程品仓计算!O91="",0,过程品仓计算!O91)+IF(过程品仓计算!P91="",0,过程品仓计算!P91)+IF(过程品仓计算!Q91="",0,过程品仓计算!Q91),0)</f>
+        <v/>
+      </c>
+      <c r="S91" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R91/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8241,18 +9217,24 @@
         <v/>
       </c>
       <c r="L92" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H92,过程品仓计算!K92),0)</f>
-        <v/>
-      </c>
-      <c r="M92" s="9" t="n"/>
-      <c r="N92" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H92,过程品仓计算!K92)/MAX(1-IF(过程品仓计算!M92="",0,过程品仓计算!M92),0.01)*(1+IF(过程品仓计算!N92="",0,过程品仓计算!N92)),0)</f>
+        <v/>
+      </c>
+      <c r="M92" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O92" s="9" t="n"/>
-      <c r="P92" s="10">
-        <f>IFERROR(过程品仓计算!L92+IF(过程品仓计算!M92="",0,过程品仓计算!M92)+IF(过程品仓计算!N92="",0,过程品仓计算!N92)+IF(过程品仓计算!O92="",0,过程品仓计算!O92),0)</f>
-        <v/>
-      </c>
-      <c r="Q92" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P92/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P92" s="9" t="n"/>
+      <c r="Q92" s="9" t="n"/>
+      <c r="R92" s="10">
+        <f>IFERROR(过程品仓计算!L92+IF(过程品仓计算!O92="",0,过程品仓计算!O92)+IF(过程品仓计算!P92="",0,过程品仓计算!P92)+IF(过程品仓计算!Q92="",0,过程品仓计算!Q92),0)</f>
+        <v/>
+      </c>
+      <c r="S92" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R92/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8298,18 +9280,24 @@
         <v/>
       </c>
       <c r="L93" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H93,过程品仓计算!K93),0)</f>
-        <v/>
-      </c>
-      <c r="M93" s="9" t="n"/>
-      <c r="N93" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H93,过程品仓计算!K93)/MAX(1-IF(过程品仓计算!M93="",0,过程品仓计算!M93),0.01)*(1+IF(过程品仓计算!N93="",0,过程品仓计算!N93)),0)</f>
+        <v/>
+      </c>
+      <c r="M93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O93" s="9" t="n"/>
-      <c r="P93" s="10">
-        <f>IFERROR(过程品仓计算!L93+IF(过程品仓计算!M93="",0,过程品仓计算!M93)+IF(过程品仓计算!N93="",0,过程品仓计算!N93)+IF(过程品仓计算!O93="",0,过程品仓计算!O93),0)</f>
-        <v/>
-      </c>
-      <c r="Q93" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P93/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P93" s="9" t="n"/>
+      <c r="Q93" s="9" t="n"/>
+      <c r="R93" s="10">
+        <f>IFERROR(过程品仓计算!L93+IF(过程品仓计算!O93="",0,过程品仓计算!O93)+IF(过程品仓计算!P93="",0,过程品仓计算!P93)+IF(过程品仓计算!Q93="",0,过程品仓计算!Q93),0)</f>
+        <v/>
+      </c>
+      <c r="S93" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R93/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8355,18 +9343,24 @@
         <v/>
       </c>
       <c r="L94" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H94,过程品仓计算!K94),0)</f>
-        <v/>
-      </c>
-      <c r="M94" s="9" t="n"/>
-      <c r="N94" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H94,过程品仓计算!K94)/MAX(1-IF(过程品仓计算!M94="",0,过程品仓计算!M94),0.01)*(1+IF(过程品仓计算!N94="",0,过程品仓计算!N94)),0)</f>
+        <v/>
+      </c>
+      <c r="M94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O94" s="9" t="n"/>
-      <c r="P94" s="10">
-        <f>IFERROR(过程品仓计算!L94+IF(过程品仓计算!M94="",0,过程品仓计算!M94)+IF(过程品仓计算!N94="",0,过程品仓计算!N94)+IF(过程品仓计算!O94="",0,过程品仓计算!O94),0)</f>
-        <v/>
-      </c>
-      <c r="Q94" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P94/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P94" s="9" t="n"/>
+      <c r="Q94" s="9" t="n"/>
+      <c r="R94" s="10">
+        <f>IFERROR(过程品仓计算!L94+IF(过程品仓计算!O94="",0,过程品仓计算!O94)+IF(过程品仓计算!P94="",0,过程品仓计算!P94)+IF(过程品仓计算!Q94="",0,过程品仓计算!Q94),0)</f>
+        <v/>
+      </c>
+      <c r="S94" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R94/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8412,18 +9406,24 @@
         <v/>
       </c>
       <c r="L95" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H95,过程品仓计算!K95),0)</f>
-        <v/>
-      </c>
-      <c r="M95" s="9" t="n"/>
-      <c r="N95" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H95,过程品仓计算!K95)/MAX(1-IF(过程品仓计算!M95="",0,过程品仓计算!M95),0.01)*(1+IF(过程品仓计算!N95="",0,过程品仓计算!N95)),0)</f>
+        <v/>
+      </c>
+      <c r="M95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O95" s="9" t="n"/>
-      <c r="P95" s="10">
-        <f>IFERROR(过程品仓计算!L95+IF(过程品仓计算!M95="",0,过程品仓计算!M95)+IF(过程品仓计算!N95="",0,过程品仓计算!N95)+IF(过程品仓计算!O95="",0,过程品仓计算!O95),0)</f>
-        <v/>
-      </c>
-      <c r="Q95" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P95/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P95" s="9" t="n"/>
+      <c r="Q95" s="9" t="n"/>
+      <c r="R95" s="10">
+        <f>IFERROR(过程品仓计算!L95+IF(过程品仓计算!O95="",0,过程品仓计算!O95)+IF(过程品仓计算!P95="",0,过程品仓计算!P95)+IF(过程品仓计算!Q95="",0,过程品仓计算!Q95),0)</f>
+        <v/>
+      </c>
+      <c r="S95" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R95/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8469,18 +9469,24 @@
         <v/>
       </c>
       <c r="L96" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H96,过程品仓计算!K96),0)</f>
-        <v/>
-      </c>
-      <c r="M96" s="9" t="n"/>
-      <c r="N96" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H96,过程品仓计算!K96)/MAX(1-IF(过程品仓计算!M96="",0,过程品仓计算!M96),0.01)*(1+IF(过程品仓计算!N96="",0,过程品仓计算!N96)),0)</f>
+        <v/>
+      </c>
+      <c r="M96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O96" s="9" t="n"/>
-      <c r="P96" s="10">
-        <f>IFERROR(过程品仓计算!L96+IF(过程品仓计算!M96="",0,过程品仓计算!M96)+IF(过程品仓计算!N96="",0,过程品仓计算!N96)+IF(过程品仓计算!O96="",0,过程品仓计算!O96),0)</f>
-        <v/>
-      </c>
-      <c r="Q96" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P96/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P96" s="9" t="n"/>
+      <c r="Q96" s="9" t="n"/>
+      <c r="R96" s="10">
+        <f>IFERROR(过程品仓计算!L96+IF(过程品仓计算!O96="",0,过程品仓计算!O96)+IF(过程品仓计算!P96="",0,过程品仓计算!P96)+IF(过程品仓计算!Q96="",0,过程品仓计算!Q96),0)</f>
+        <v/>
+      </c>
+      <c r="S96" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R96/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8526,18 +9532,24 @@
         <v/>
       </c>
       <c r="L97" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H97,过程品仓计算!K97),0)</f>
-        <v/>
-      </c>
-      <c r="M97" s="9" t="n"/>
-      <c r="N97" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H97,过程品仓计算!K97)/MAX(1-IF(过程品仓计算!M97="",0,过程品仓计算!M97),0.01)*(1+IF(过程品仓计算!N97="",0,过程品仓计算!N97)),0)</f>
+        <v/>
+      </c>
+      <c r="M97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O97" s="9" t="n"/>
-      <c r="P97" s="10">
-        <f>IFERROR(过程品仓计算!L97+IF(过程品仓计算!M97="",0,过程品仓计算!M97)+IF(过程品仓计算!N97="",0,过程品仓计算!N97)+IF(过程品仓计算!O97="",0,过程品仓计算!O97),0)</f>
-        <v/>
-      </c>
-      <c r="Q97" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P97/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P97" s="9" t="n"/>
+      <c r="Q97" s="9" t="n"/>
+      <c r="R97" s="10">
+        <f>IFERROR(过程品仓计算!L97+IF(过程品仓计算!O97="",0,过程品仓计算!O97)+IF(过程品仓计算!P97="",0,过程品仓计算!P97)+IF(过程品仓计算!Q97="",0,过程品仓计算!Q97),0)</f>
+        <v/>
+      </c>
+      <c r="S97" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R97/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8583,18 +9595,24 @@
         <v/>
       </c>
       <c r="L98" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H98,过程品仓计算!K98),0)</f>
-        <v/>
-      </c>
-      <c r="M98" s="9" t="n"/>
-      <c r="N98" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H98,过程品仓计算!K98)/MAX(1-IF(过程品仓计算!M98="",0,过程品仓计算!M98),0.01)*(1+IF(过程品仓计算!N98="",0,过程品仓计算!N98)),0)</f>
+        <v/>
+      </c>
+      <c r="M98" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O98" s="9" t="n"/>
-      <c r="P98" s="10">
-        <f>IFERROR(过程品仓计算!L98+IF(过程品仓计算!M98="",0,过程品仓计算!M98)+IF(过程品仓计算!N98="",0,过程品仓计算!N98)+IF(过程品仓计算!O98="",0,过程品仓计算!O98),0)</f>
-        <v/>
-      </c>
-      <c r="Q98" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P98/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P98" s="9" t="n"/>
+      <c r="Q98" s="9" t="n"/>
+      <c r="R98" s="10">
+        <f>IFERROR(过程品仓计算!L98+IF(过程品仓计算!O98="",0,过程品仓计算!O98)+IF(过程品仓计算!P98="",0,过程品仓计算!P98)+IF(过程品仓计算!Q98="",0,过程品仓计算!Q98),0)</f>
+        <v/>
+      </c>
+      <c r="S98" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R98/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8640,18 +9658,24 @@
         <v/>
       </c>
       <c r="L99" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H99,过程品仓计算!K99),0)</f>
-        <v/>
-      </c>
-      <c r="M99" s="9" t="n"/>
-      <c r="N99" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H99,过程品仓计算!K99)/MAX(1-IF(过程品仓计算!M99="",0,过程品仓计算!M99),0.01)*(1+IF(过程品仓计算!N99="",0,过程品仓计算!N99)),0)</f>
+        <v/>
+      </c>
+      <c r="M99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O99" s="9" t="n"/>
-      <c r="P99" s="10">
-        <f>IFERROR(过程品仓计算!L99+IF(过程品仓计算!M99="",0,过程品仓计算!M99)+IF(过程品仓计算!N99="",0,过程品仓计算!N99)+IF(过程品仓计算!O99="",0,过程品仓计算!O99),0)</f>
-        <v/>
-      </c>
-      <c r="Q99" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P99/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P99" s="9" t="n"/>
+      <c r="Q99" s="9" t="n"/>
+      <c r="R99" s="10">
+        <f>IFERROR(过程品仓计算!L99+IF(过程品仓计算!O99="",0,过程品仓计算!O99)+IF(过程品仓计算!P99="",0,过程品仓计算!P99)+IF(过程品仓计算!Q99="",0,过程品仓计算!Q99),0)</f>
+        <v/>
+      </c>
+      <c r="S99" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R99/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8697,18 +9721,24 @@
         <v/>
       </c>
       <c r="L100" s="10">
-        <f>IFERROR(MAX(过程品仓计算!H100,过程品仓计算!K100),0)</f>
-        <v/>
-      </c>
-      <c r="M100" s="9" t="n"/>
-      <c r="N100" s="9" t="n"/>
+        <f>IFERROR(MAX(过程品仓计算!H100,过程品仓计算!K100)/MAX(1-IF(过程品仓计算!M100="",0,过程品仓计算!M100),0.01)*(1+IF(过程品仓计算!N100="",0,过程品仓计算!N100)),0)</f>
+        <v/>
+      </c>
+      <c r="M100" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="O100" s="9" t="n"/>
-      <c r="P100" s="10">
-        <f>IFERROR(过程品仓计算!L100+IF(过程品仓计算!M100="",0,过程品仓计算!M100)+IF(过程品仓计算!N100="",0,过程品仓计算!N100)+IF(过程品仓计算!O100="",0,过程品仓计算!O100),0)</f>
-        <v/>
-      </c>
-      <c r="Q100" s="10">
-        <f>IFERROR(CEILING(过程品仓计算!P100/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
+      <c r="P100" s="9" t="n"/>
+      <c r="Q100" s="9" t="n"/>
+      <c r="R100" s="10">
+        <f>IFERROR(过程品仓计算!L100+IF(过程品仓计算!O100="",0,过程品仓计算!O100)+IF(过程品仓计算!P100="",0,过程品仓计算!P100)+IF(过程品仓计算!Q100="",0,过程品仓计算!Q100),0)</f>
+        <v/>
+      </c>
+      <c r="S100" s="10">
+        <f>IFERROR(CEILING(过程品仓计算!R100/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$18*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -8718,12 +9748,12 @@
           <t>成品筛分后暂存（成品前） 小计</t>
         </is>
       </c>
-      <c r="P101" s="10">
-        <f>SUM(P89:P100)</f>
-        <v/>
-      </c>
-      <c r="Q101" s="10">
-        <f>SUM(Q89:Q100)</f>
+      <c r="R101" s="10">
+        <f>SUM(R89:R100)</f>
+        <v/>
+      </c>
+      <c r="S101" s="10">
+        <f>SUM(S89:S100)</f>
         <v/>
       </c>
     </row>
@@ -8733,34 +9763,34 @@
           <t>过程品仓 合计</t>
         </is>
       </c>
-      <c r="P102" s="10">
-        <f>SUMPRODUCT((MOD(ROW(P4:P101)-4,14)=(13))*P4:P101)</f>
-        <v/>
-      </c>
-      <c r="Q102" s="10">
-        <f>SUMPRODUCT((MOD(ROW(Q4:Q101)-4,14)=(13))*Q4:Q101)</f>
+      <c r="R102" s="10">
+        <f>SUMPRODUCT((MOD(ROW(R4:R101)-4,14)=(13))*R4:R101)</f>
+        <v/>
+      </c>
+      <c r="S102" s="10">
+        <f>SUMPRODUCT((MOD(ROW(S4:S101)-4,14)=(13))*S4:S101)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A87:O87"/>
-    <mergeCell ref="A59:O59"/>
-    <mergeCell ref="A74:Q74"/>
-    <mergeCell ref="A88:Q88"/>
-    <mergeCell ref="A18:Q18"/>
-    <mergeCell ref="A73:O73"/>
-    <mergeCell ref="A101:O101"/>
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A102:O102"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A45:O45"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A60:Q60"/>
-    <mergeCell ref="A17:O17"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A46:Q46"/>
-    <mergeCell ref="A32:Q32"/>
+    <mergeCell ref="A31:Q31"/>
+    <mergeCell ref="A60:S60"/>
+    <mergeCell ref="A17:Q17"/>
+    <mergeCell ref="A46:S46"/>
+    <mergeCell ref="A32:S32"/>
+    <mergeCell ref="A87:Q87"/>
+    <mergeCell ref="A59:Q59"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A74:S74"/>
+    <mergeCell ref="A18:S18"/>
+    <mergeCell ref="A73:Q73"/>
+    <mergeCell ref="A88:S88"/>
+    <mergeCell ref="A101:Q101"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A45:Q45"/>
+    <mergeCell ref="A102:Q102"/>
+    <mergeCell ref="A2:S2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8773,7 +9803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8788,9 +9818,11 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -8803,7 +9835,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>公式：设计库存 = MAX(日需求×生产间隔, 日需求×目标库存天数, 最小生产批量) + 安全库存(日需求×安全天数) + 待检放行库存</t>
+          <t>公式：设计库存 = MAX(日需求×生产间隔, 日需求×目标库存天数, 最小生产批量) + 安全库存(日需求×安全天数) + 返工补偿库存 + 待检放行库存</t>
         </is>
       </c>
     </row>
@@ -8885,18 +9917,30 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
+          <t>返工率</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>返工补偿
+库存
+[自动]</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
           <t>待检放行
 库存</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>设计库存
 合计
 [自动]</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>估算占地
 面积(m²)
@@ -8952,13 +9996,21 @@
         <f>IFERROR(成品仓计算!E4*产品SKU!K3*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M4" s="9" t="n"/>
+      <c r="M4" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N4" s="10">
-        <f>IFERROR(成品仓计算!K4+成品仓计算!L4+IF(成品仓计算!M4="",0,成品仓计算!M4),0)</f>
-        <v/>
-      </c>
-      <c r="O4" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N4/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K4*成品仓计算!M4,0)</f>
+        <v/>
+      </c>
+      <c r="O4" s="9" t="n"/>
+      <c r="P4" s="10">
+        <f>IFERROR(成品仓计算!K4+成品仓计算!L4+成品仓计算!N4+IF(成品仓计算!O4="",0,成品仓计算!O4),0)</f>
+        <v/>
+      </c>
+      <c r="Q4" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P4/MAX(产品SKU!M3,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9010,13 +10062,21 @@
         <f>IFERROR(成品仓计算!E5*产品SKU!K4*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M5" s="9" t="n"/>
+      <c r="M5" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N5" s="10">
-        <f>IFERROR(成品仓计算!K5+成品仓计算!L5+IF(成品仓计算!M5="",0,成品仓计算!M5),0)</f>
-        <v/>
-      </c>
-      <c r="O5" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N5/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K5*成品仓计算!M5,0)</f>
+        <v/>
+      </c>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="10">
+        <f>IFERROR(成品仓计算!K5+成品仓计算!L5+成品仓计算!N5+IF(成品仓计算!O5="",0,成品仓计算!O5),0)</f>
+        <v/>
+      </c>
+      <c r="Q5" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P5/MAX(产品SKU!M4,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9068,13 +10128,21 @@
         <f>IFERROR(成品仓计算!E6*产品SKU!K5*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M6" s="9" t="n"/>
+      <c r="M6" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N6" s="10">
-        <f>IFERROR(成品仓计算!K6+成品仓计算!L6+IF(成品仓计算!M6="",0,成品仓计算!M6),0)</f>
-        <v/>
-      </c>
-      <c r="O6" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N6/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K6*成品仓计算!M6,0)</f>
+        <v/>
+      </c>
+      <c r="O6" s="9" t="n"/>
+      <c r="P6" s="10">
+        <f>IFERROR(成品仓计算!K6+成品仓计算!L6+成品仓计算!N6+IF(成品仓计算!O6="",0,成品仓计算!O6),0)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P6/MAX(产品SKU!M5,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9126,13 +10194,21 @@
         <f>IFERROR(成品仓计算!E7*产品SKU!K6*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M7" s="9" t="n"/>
+      <c r="M7" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N7" s="10">
-        <f>IFERROR(成品仓计算!K7+成品仓计算!L7+IF(成品仓计算!M7="",0,成品仓计算!M7),0)</f>
-        <v/>
-      </c>
-      <c r="O7" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N7/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K7*成品仓计算!M7,0)</f>
+        <v/>
+      </c>
+      <c r="O7" s="9" t="n"/>
+      <c r="P7" s="10">
+        <f>IFERROR(成品仓计算!K7+成品仓计算!L7+成品仓计算!N7+IF(成品仓计算!O7="",0,成品仓计算!O7),0)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P7/MAX(产品SKU!M6,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9184,13 +10260,21 @@
         <f>IFERROR(成品仓计算!E8*产品SKU!K7*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M8" s="9" t="n"/>
+      <c r="M8" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N8" s="10">
-        <f>IFERROR(成品仓计算!K8+成品仓计算!L8+IF(成品仓计算!M8="",0,成品仓计算!M8),0)</f>
-        <v/>
-      </c>
-      <c r="O8" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N8/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K8*成品仓计算!M8,0)</f>
+        <v/>
+      </c>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="10">
+        <f>IFERROR(成品仓计算!K8+成品仓计算!L8+成品仓计算!N8+IF(成品仓计算!O8="",0,成品仓计算!O8),0)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P8/MAX(产品SKU!M7,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9242,13 +10326,21 @@
         <f>IFERROR(成品仓计算!E9*产品SKU!K8*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M9" s="9" t="n"/>
+      <c r="M9" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N9" s="10">
-        <f>IFERROR(成品仓计算!K9+成品仓计算!L9+IF(成品仓计算!M9="",0,成品仓计算!M9),0)</f>
-        <v/>
-      </c>
-      <c r="O9" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N9/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K9*成品仓计算!M9,0)</f>
+        <v/>
+      </c>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="10">
+        <f>IFERROR(成品仓计算!K9+成品仓计算!L9+成品仓计算!N9+IF(成品仓计算!O9="",0,成品仓计算!O9),0)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P9/MAX(产品SKU!M8,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9300,13 +10392,21 @@
         <f>IFERROR(成品仓计算!E10*产品SKU!K9*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M10" s="9" t="n"/>
+      <c r="M10" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N10" s="10">
-        <f>IFERROR(成品仓计算!K10+成品仓计算!L10+IF(成品仓计算!M10="",0,成品仓计算!M10),0)</f>
-        <v/>
-      </c>
-      <c r="O10" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N10/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K10*成品仓计算!M10,0)</f>
+        <v/>
+      </c>
+      <c r="O10" s="9" t="n"/>
+      <c r="P10" s="10">
+        <f>IFERROR(成品仓计算!K10+成品仓计算!L10+成品仓计算!N10+IF(成品仓计算!O10="",0,成品仓计算!O10),0)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P10/MAX(产品SKU!M9,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9358,13 +10458,21 @@
         <f>IFERROR(成品仓计算!E11*产品SKU!K10*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M11" s="9" t="n"/>
+      <c r="M11" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N11" s="10">
-        <f>IFERROR(成品仓计算!K11+成品仓计算!L11+IF(成品仓计算!M11="",0,成品仓计算!M11),0)</f>
-        <v/>
-      </c>
-      <c r="O11" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N11/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K11*成品仓计算!M11,0)</f>
+        <v/>
+      </c>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="10">
+        <f>IFERROR(成品仓计算!K11+成品仓计算!L11+成品仓计算!N11+IF(成品仓计算!O11="",0,成品仓计算!O11),0)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P11/MAX(产品SKU!M10,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9416,13 +10524,21 @@
         <f>IFERROR(成品仓计算!E12*产品SKU!K11*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M12" s="9" t="n"/>
+      <c r="M12" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N12" s="10">
-        <f>IFERROR(成品仓计算!K12+成品仓计算!L12+IF(成品仓计算!M12="",0,成品仓计算!M12),0)</f>
-        <v/>
-      </c>
-      <c r="O12" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N12/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K12*成品仓计算!M12,0)</f>
+        <v/>
+      </c>
+      <c r="O12" s="9" t="n"/>
+      <c r="P12" s="10">
+        <f>IFERROR(成品仓计算!K12+成品仓计算!L12+成品仓计算!N12+IF(成品仓计算!O12="",0,成品仓计算!O12),0)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P12/MAX(产品SKU!M11,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9474,13 +10590,21 @@
         <f>IFERROR(成品仓计算!E13*产品SKU!K12*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M13" s="9" t="n"/>
+      <c r="M13" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N13" s="10">
-        <f>IFERROR(成品仓计算!K13+成品仓计算!L13+IF(成品仓计算!M13="",0,成品仓计算!M13),0)</f>
-        <v/>
-      </c>
-      <c r="O13" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N13/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K13*成品仓计算!M13,0)</f>
+        <v/>
+      </c>
+      <c r="O13" s="9" t="n"/>
+      <c r="P13" s="10">
+        <f>IFERROR(成品仓计算!K13+成品仓计算!L13+成品仓计算!N13+IF(成品仓计算!O13="",0,成品仓计算!O13),0)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P13/MAX(产品SKU!M12,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9532,13 +10656,21 @@
         <f>IFERROR(成品仓计算!E14*产品SKU!K13*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M14" s="9" t="n"/>
+      <c r="M14" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N14" s="10">
-        <f>IFERROR(成品仓计算!K14+成品仓计算!L14+IF(成品仓计算!M14="",0,成品仓计算!M14),0)</f>
-        <v/>
-      </c>
-      <c r="O14" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N14/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K14*成品仓计算!M14,0)</f>
+        <v/>
+      </c>
+      <c r="O14" s="9" t="n"/>
+      <c r="P14" s="10">
+        <f>IFERROR(成品仓计算!K14+成品仓计算!L14+成品仓计算!N14+IF(成品仓计算!O14="",0,成品仓计算!O14),0)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P14/MAX(产品SKU!M13,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9590,13 +10722,21 @@
         <f>IFERROR(成品仓计算!E15*产品SKU!K14*参数设置!$C$9,0)</f>
         <v/>
       </c>
-      <c r="M15" s="9" t="n"/>
+      <c r="M15" s="10">
+        <f>参数设置!$C$30</f>
+        <v/>
+      </c>
       <c r="N15" s="10">
-        <f>IFERROR(成品仓计算!K15+成品仓计算!L15+IF(成品仓计算!M15="",0,成品仓计算!M15),0)</f>
-        <v/>
-      </c>
-      <c r="O15" s="10">
-        <f>IFERROR(CEILING(成品仓计算!N15/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
+        <f>IFERROR(成品仓计算!K15*成品仓计算!M15,0)</f>
+        <v/>
+      </c>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="10">
+        <f>IFERROR(成品仓计算!K15+成品仓计算!L15+成品仓计算!N15+IF(成品仓计算!O15="",0,成品仓计算!O15),0)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="10">
+        <f>IFERROR(CEILING(成品仓计算!P15/MAX(产品SKU!M14,1),1)*参数设置!$C$13/MAX(参数设置!$C$14,1)/参数设置!$C$19*参数设置!$C$21,0)</f>
         <v/>
       </c>
     </row>
@@ -9606,20 +10746,20 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="N16" s="10">
-        <f>SUM(N4:N15)</f>
-        <v/>
-      </c>
-      <c r="O16" s="10">
-        <f>SUM(O4:O15)</f>
+      <c r="P16" s="10">
+        <f>SUM(P4:P15)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="10">
+        <f>SUM(Q4:Q15)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9632,7 +10772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -9642,7 +10782,9 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -9695,6 +10837,19 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
+          <t>估算库存
+单价(元)</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>库存占用
+金额(元)
+[自动]</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
@@ -9711,7 +10866,7 @@
         </is>
       </c>
       <c r="C3" s="10">
-        <f>原料仓计算!M19</f>
+        <f>原料仓计算!R19</f>
         <v/>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -9720,18 +10875,23 @@
         </is>
       </c>
       <c r="E3" s="17">
-        <f>原料仓计算!O19</f>
+        <f>原料仓计算!T19</f>
         <v/>
       </c>
       <c r="F3" s="10">
-        <f>原料仓计算!P19</f>
+        <f>原料仓计算!U19</f>
         <v/>
       </c>
       <c r="G3" s="10">
         <f>IFERROR(汇总!F3*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H3" s="8" t="inlineStr"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="10">
+        <f>IFERROR(汇总!C3*汇总!H3,0)</f>
+        <v/>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
@@ -9742,11 +10902,11 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次) + 待检 + 尾批 + 不良品</t>
+          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次)÷(1-故障率)×(1+良率损失率) + 待检 + 尾批 + 不良品</t>
         </is>
       </c>
       <c r="C4" s="10">
-        <f>过程品仓计算!P17</f>
+        <f>过程品仓计算!R17</f>
         <v/>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -9756,14 +10916,19 @@
       </c>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="10">
-        <f>过程品仓计算!Q17</f>
+        <f>过程品仓计算!S17</f>
         <v/>
       </c>
       <c r="G4" s="10">
         <f>IFERROR(汇总!F4*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="10">
+        <f>IFERROR(汇总!C4*汇总!H4,0)</f>
+        <v/>
+      </c>
+      <c r="J4" s="8" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
@@ -9774,11 +10939,11 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次) + 待检 + 尾批 + 不良品</t>
+          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次)÷(1-故障率)×(1+良率损失率) + 待检 + 尾批 + 不良品</t>
         </is>
       </c>
       <c r="C5" s="10">
-        <f>过程品仓计算!P31</f>
+        <f>过程品仓计算!R31</f>
         <v/>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -9788,14 +10953,19 @@
       </c>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="10">
-        <f>过程品仓计算!Q31</f>
+        <f>过程品仓计算!S31</f>
         <v/>
       </c>
       <c r="G5" s="10">
         <f>IFERROR(汇总!F5*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="10">
+        <f>IFERROR(汇总!C5*汇总!H5,0)</f>
+        <v/>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
@@ -9806,11 +10976,11 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次) + 待检 + 尾批 + 不良品</t>
+          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次)÷(1-故障率)×(1+良率损失率) + 待检 + 尾批 + 不良品</t>
         </is>
       </c>
       <c r="C6" s="10">
-        <f>过程品仓计算!P45</f>
+        <f>过程品仓计算!R45</f>
         <v/>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -9820,14 +10990,19 @@
       </c>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10">
-        <f>过程品仓计算!Q45</f>
+        <f>过程品仓计算!S45</f>
         <v/>
       </c>
       <c r="G6" s="10">
         <f>IFERROR(汇总!F6*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="10">
+        <f>IFERROR(汇总!C6*汇总!H6,0)</f>
+        <v/>
+      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
@@ -9838,11 +11013,11 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次) + 待检 + 尾批 + 不良品</t>
+          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次)÷(1-故障率)×(1+良率损失率) + 待检 + 尾批 + 不良品</t>
         </is>
       </c>
       <c r="C7" s="10">
-        <f>过程品仓计算!P59</f>
+        <f>过程品仓计算!R59</f>
         <v/>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -9852,14 +11027,19 @@
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10">
-        <f>过程品仓计算!Q59</f>
+        <f>过程品仓计算!S59</f>
         <v/>
       </c>
       <c r="G7" s="10">
         <f>IFERROR(汇总!F7*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="10">
+        <f>IFERROR(汇总!C7*汇总!H7,0)</f>
+        <v/>
+      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="21" t="inlineStr">
@@ -9870,11 +11050,11 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次) + 待检 + 尾批 + 不良品</t>
+          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次)÷(1-故障率)×(1+良率损失率) + 待检 + 尾批 + 不良品</t>
         </is>
       </c>
       <c r="C8" s="10">
-        <f>过程品仓计算!P73</f>
+        <f>过程品仓计算!R73</f>
         <v/>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -9884,14 +11064,19 @@
       </c>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10">
-        <f>过程品仓计算!Q73</f>
+        <f>过程品仓计算!S73</f>
         <v/>
       </c>
       <c r="G8" s="10">
         <f>IFERROR(汇总!F8*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="10">
+        <f>IFERROR(汇总!C8*汇总!H8,0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="20" t="inlineStr">
@@ -9902,11 +11087,11 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次) + 待检 + 尾批 + 不良品</t>
+          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次)÷(1-故障率)×(1+良率损失率) + 待检 + 尾批 + 不良品</t>
         </is>
       </c>
       <c r="C9" s="10">
-        <f>过程品仓计算!P87</f>
+        <f>过程品仓计算!R87</f>
         <v/>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -9916,14 +11101,19 @@
       </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10">
-        <f>过程品仓计算!Q87</f>
+        <f>过程品仓计算!S87</f>
         <v/>
       </c>
       <c r="G9" s="10">
         <f>IFERROR(汇总!F9*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="10">
+        <f>IFERROR(汇总!C9*汇总!H9,0)</f>
+        <v/>
+      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="21" t="inlineStr">
@@ -9934,11 +11124,11 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次) + 待检 + 尾批 + 不良品</t>
+          <t>MAX(下游小时消耗×缓冲小时数, 批量×等待批次)÷(1-故障率)×(1+良率损失率) + 待检 + 尾批 + 不良品</t>
         </is>
       </c>
       <c r="C10" s="10">
-        <f>过程品仓计算!P101</f>
+        <f>过程品仓计算!R101</f>
         <v/>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -9948,14 +11138,19 @@
       </c>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10">
-        <f>过程品仓计算!Q101</f>
+        <f>过程品仓计算!S101</f>
         <v/>
       </c>
       <c r="G10" s="10">
         <f>IFERROR(汇总!F10*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="10">
+        <f>IFERROR(汇总!C10*汇总!H10,0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
@@ -9965,11 +11160,11 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>见过程品仓计算!P102</t>
+          <t>见过程品仓计算!R102</t>
         </is>
       </c>
       <c r="C11" s="10">
-        <f>过程品仓计算!P102</f>
+        <f>过程品仓计算!R102</f>
         <v/>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -9979,14 +11174,19 @@
       </c>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10">
-        <f>过程品仓计算!Q102</f>
+        <f>过程品仓计算!S102</f>
         <v/>
       </c>
       <c r="G11" s="10">
         <f>IFERROR(汇总!F11*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="10">
+        <f>IFERROR(汇总!C11*汇总!H11,0)</f>
+        <v/>
+      </c>
+      <c r="J11" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
@@ -9996,11 +11196,11 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>MAX(日需求×生产间隔, 日需求×目标天数, 最小批量) + 安全库存 + 待检放行</t>
+          <t>MAX(日需求×生产间隔, 日需求×目标天数, 最小批量) + 安全库存 + 返工补偿 + 待检放行</t>
         </is>
       </c>
       <c r="C12" s="10">
-        <f>成品仓计算!N16</f>
+        <f>成品仓计算!P16</f>
         <v/>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -10010,14 +11210,19 @@
       </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10">
-        <f>成品仓计算!O16</f>
+        <f>成品仓计算!Q16</f>
         <v/>
       </c>
       <c r="G12" s="10">
         <f>IFERROR(汇总!F12*参数设置!$C$21,0)</f>
         <v/>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="10">
+        <f>IFERROR(汇总!C12*汇总!H12,0)</f>
+        <v/>
+      </c>
+      <c r="J12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
@@ -10029,6 +11234,10 @@
         <f>IFERROR(汇总!G3+汇总!G11+汇总!G12,0)</f>
         <v/>
       </c>
+      <c r="I13" s="10">
+        <f>IFERROR(汇总!I3+汇总!I11+汇总!I12,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -10112,10 +11321,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:J17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
